--- a/outputs/Mukaさん_外注テストケース_2026-06-12.xlsx
+++ b/outputs/Mukaさん_外注テストケース_2026-06-12.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_概要" sheetId="1" r:id="Re976f5081d2642d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_事前説明" sheetId="2" r:id="R882983aa5be6430c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_基本操作" sheetId="3" r:id="Ree22fafbfdb048c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_ランダム問題" sheetId="4" r:id="R008b09d1c71f458e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_要望回帰" sheetId="5" r:id="R813d3b3d16a84ee6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_バグ報告" sheetId="6" r:id="R0a8325c4672b4d03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_概要" sheetId="1" r:id="R87c1dfe53ab640fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_事前説明" sheetId="2" r:id="R48cc71de191d49bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_基本操作" sheetId="3" r:id="R2c10618b3c67438d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_ランダム問題" sheetId="4" r:id="Rb77c857a74d042a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_要望回帰" sheetId="5" r:id="R2d0e4715de934e09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_バグ報告" sheetId="6" r:id="R266dd85221164df9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -303,7 +303,7 @@
         <x:v>ランダム問題件数</x:v>
       </x:c>
       <x:c r="B9" t="str">
-        <x:v>45</x:v>
+        <x:v>45パート</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -327,7 +327,7 @@
         <x:v>抽出条件</x:v>
       </x:c>
       <x:c r="B12" t="str">
-        <x:v>機能・仕様要望/不具合・改善報告は2026-03-14以降を全件。問題ランダムは各学年15件、うちコンテンツ修正対象を優先混入。</x:v>
+        <x:v>機能・仕様要望/不具合・改善報告は2026-03-14以降を全件。ランダム問題は各学年15パート、合計45パートを抽出し、各パートを最初から最後まで確認。コンテンツ修正対象パートを優先混入。</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -402,7 +402,7 @@
       </x:c>
       <x:c r="B6" t="str">
         <x:v>02_基本操作: 16件
-03_ランダム問題: 45件
+03_ランダム問題: 45パート
 04_要望回帰: 19件
 合計: 80件</x:v>
       </x:c>
@@ -1089,13 +1089,13 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
-        <x:v>RQ-001</x:v>
+        <x:v>RP-001</x:v>
       </x:c>
       <x:c r="B2" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>学年1 / パート14-2 / 1-14-2-5</x:v>
+        <x:v>学年1 / パート3-2 / 1-3-2</x:v>
       </x:c>
       <x:c r="D2" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -1103,22 +1103,24 @@
       <x:c r="E2" t="str">
         <x:v>1. ログインする
 2. 学年1を選ぶ
-3. パート14-2を選んで開始する
-4. 表示順5の問題まで進める（途中で間違えてもOK）
-5. 表示順5の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート3-2を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F2" t="str">
-        <x:v>問題文: Whose chairs are those?
-期待解答: They are our chairs.
-画像: /questions/1_14_2_05.png
-指示文: 「だれの～ですか？」の問いに、 「それは（私の、彼女の…）～です。」と答えましょう。</x:v>
+        <x:v>このパート全体（1-3-2 / 全8問）を最後まで通して確認する。
+最初の問題文: I am your mother.
+最初の期待解答: I'm your mother.
+画像: 画像なしのパート
+指示文: 文章を 「I'm〜」などの短縮形を使って言い直しましょう。</x:v>
       </x:c>
       <x:c r="G2" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H2" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I2" t="str"/>
       <x:c r="J2" t="str"/>
@@ -1126,13 +1128,13 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
-        <x:v>RQ-002</x:v>
+        <x:v>RP-002</x:v>
       </x:c>
       <x:c r="B3" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C3" t="str">
-        <x:v>学年1 / パート17-1 / 1-17-1-4</x:v>
+        <x:v>学年1 / パート5-1 / 1-5-1</x:v>
       </x:c>
       <x:c r="D3" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -1140,22 +1142,24 @@
       <x:c r="E3" t="str">
         <x:v>1. ログインする
 2. 学年1を選ぶ
-3. パート17-1を選んで開始する
-4. 表示順4の問題まで進める（途中で間違えてもOK）
-5. 表示順4の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート5-1を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F3" t="str">
-        <x:v>問題文: She helps her mother.
-期待解答: She helps her mother after school.
-画像: /questions/1_17_1_04.png
-指示文: 情報をプラスして文章を完成させましょう。</x:v>
+        <x:v>このパート全体（1-5-1 / 全8問）を最後まで通して確認する。
+最初の問題文: I
+最初の期待解答: I am in the kitchen.
+画像: 8問で画像あり
+指示文: 例にならい、【～は台所にいます。】 という文章を作りましょう。ただし主語はHe,She などの代名詞で答えること。</x:v>
       </x:c>
       <x:c r="G3" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H3" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I3" t="str"/>
       <x:c r="J3" t="str"/>
@@ -1163,13 +1167,13 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
-        <x:v>RQ-003</x:v>
+        <x:v>RP-003</x:v>
       </x:c>
       <x:c r="B4" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>学年1 / パート20-1 / 1-20-1-6</x:v>
+        <x:v>学年1 / パート8-2 / 1-8-2</x:v>
       </x:c>
       <x:c r="D4" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -1177,22 +1181,24 @@
       <x:c r="E4" t="str">
         <x:v>1. ログインする
 2. 学年1を選ぶ
-3. パート20-1を選んで開始する
-4. 表示順6の問題まで進める（途中で間違えてもOK）
-5. 表示順6の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート8-2を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F4" t="str">
-        <x:v>問題文: She asks her teacher a question.
-期待解答: She doesn't ask her teacher a question.
-画像: 画像なしで問題なし
-指示文: 肯定文を否定文に言いかえましょう。</x:v>
+        <x:v>このパート全体（1-8-2 / 全8問）を最後まで通して確認する。
+最初の問題文: Tom studies English.
+最初の期待解答: Yes.
+画像: 画像なしのパート
+指示文: 例にならい、3人称単数の文は Yes、 それ以外は No と答えましょう。</x:v>
       </x:c>
       <x:c r="G4" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H4" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I4" t="str"/>
       <x:c r="J4" t="str"/>
@@ -1200,13 +1206,13 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="str">
-        <x:v>RQ-004</x:v>
+        <x:v>RP-004</x:v>
       </x:c>
       <x:c r="B5" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C5" t="str">
-        <x:v>学年1 / パート20-1 / 1-20-1-8</x:v>
+        <x:v>学年1 / パート9-1 / 1-9-1</x:v>
       </x:c>
       <x:c r="D5" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -1214,22 +1220,24 @@
       <x:c r="E5" t="str">
         <x:v>1. ログインする
 2. 学年1を選ぶ
-3. パート20-1を選んで開始する
-4. 表示順8の問題まで進める（途中で間違えてもOK）
-5. 表示順8の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート9-1を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F5" t="str">
-        <x:v>問題文: She writes a letter.
-期待解答: She doesn't write a letter.
-画像: 画像なしで問題なし
-指示文: 肯定文を否定文に言いかえましょう。</x:v>
+        <x:v>このパート全体（1-9-1 / 全8問）を最後まで通して確認する。
+最初の問題文: You
+最初の期待解答: You speak English.
+画像: 8問で画像あり
+指示文: 例にならい、 「～は英語を話します。」　 という文章を完成させましょう。 ただし、主語は代名詞で答えること。</x:v>
       </x:c>
       <x:c r="G5" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H5" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I5" t="str"/>
       <x:c r="J5" t="str"/>
@@ -1237,13 +1245,13 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="str">
-        <x:v>RQ-005</x:v>
+        <x:v>RP-005</x:v>
       </x:c>
       <x:c r="B6" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C6" t="str">
-        <x:v>学年1 / パート23-1 / 1-23-1-7</x:v>
+        <x:v>学年1 / パート11-2 / 1-11-2</x:v>
       </x:c>
       <x:c r="D6" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -1251,22 +1259,24 @@
       <x:c r="E6" t="str">
         <x:v>1. ログインする
 2. 学年1を選ぶ
-3. パート23-1を選んで開始する
-4. 表示順7の問題まで進める（途中で間違えてもOK）
-5. 表示順7の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート11-2を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F6" t="str">
-        <x:v>問題文: Is it a pen?
-期待解答: Yes, it is. It is a pen.
-画像: /questions/1_23_1_07.png
-指示文: イラストの指示に従い、 Yes, またはNo,で質問に答えましょう。</x:v>
+        <x:v>このパート全体（1-11-2 / 全8問）を最後まで通して確認する。
+最初の問題文: Takuya and I
+最初の期待解答: We eat breakfast.
+画像: 8問で画像あり
+指示文: イラストを見て、主語に合う文章を考えましょう。</x:v>
       </x:c>
       <x:c r="G6" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H6" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I6" t="str"/>
       <x:c r="J6" t="str"/>
@@ -1274,13 +1284,13 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
-        <x:v>RQ-006</x:v>
+        <x:v>RP-006</x:v>
       </x:c>
       <x:c r="B7" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C7" t="str">
-        <x:v>学年1 / パート28-1 / 1-28-1-7</x:v>
+        <x:v>学年1 / パート14-2 / 1-14-2</x:v>
       </x:c>
       <x:c r="D7" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -1288,22 +1298,24 @@
       <x:c r="E7" t="str">
         <x:v>1. ログインする
 2. 学年1を選ぶ
-3. パート28-1を選んで開始する
-4. 表示順7の問題まで進める（途中で間違えてもOK）
-5. 表示順7の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート14-2を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F7" t="str">
-        <x:v>問題文: Can he ride a bike?
-期待解答: No, he can't.
-画像: /questions/1_28_1_07.png
-指示文: 例にならい、 Yes, ～ can. / No, ～ can't. で答えましょう。</x:v>
+        <x:v>このパート全体（1-14-2 / 全8問）を最後まで通して確認する。
+最初の問題文: Whose watch is this?
+最初の期待解答: It is his watch.
+画像: 8問で画像あり
+指示文: 「だれの～ですか？」の問いに、 「それは（私の、彼女の…）～です。」と答えましょう。</x:v>
       </x:c>
       <x:c r="G7" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H7" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I7" t="str"/>
       <x:c r="J7" t="str"/>
@@ -1311,13 +1323,13 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="str">
-        <x:v>RQ-007</x:v>
+        <x:v>RP-007</x:v>
       </x:c>
       <x:c r="B8" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C8" t="str">
-        <x:v>学年1 / パート29-1 / 1-29-1-3</x:v>
+        <x:v>学年1 / パート18-2 / 1-18-2</x:v>
       </x:c>
       <x:c r="D8" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -1325,22 +1337,24 @@
       <x:c r="E8" t="str">
         <x:v>1. ログインする
 2. 学年1を選ぶ
-3. パート29-1を選んで開始する
-4. 表示順3の問題まで進める（途中で間違えてもOK）
-5. 表示順3の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート18-2を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F8" t="str">
-        <x:v>問題文: Use this pen
-期待解答: Can I use this pen?
-画像: 画像なしで問題なし
-指示文: 例にならい、 「〜してもいいですか？」の文に言いかえましょう。</x:v>
+        <x:v>このパート全体（1-18-2 / 全8問）を最後まで通して確認する。
+最初の問題文: I am a doctor.
+最初の期待解答: I am not a doctor.
+画像: 画像なしのパート
+指示文: 肯定文を否定文に言いかえましょう。</x:v>
       </x:c>
       <x:c r="G8" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H8" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I8" t="str"/>
       <x:c r="J8" t="str"/>
@@ -1348,13 +1362,13 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="str">
-        <x:v>RQ-008</x:v>
+        <x:v>RP-008</x:v>
       </x:c>
       <x:c r="B9" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C9" t="str">
-        <x:v>学年1 / パート33-2 / 1-33-2-6</x:v>
+        <x:v>学年1 / パート19-1 / 1-19-1</x:v>
       </x:c>
       <x:c r="D9" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -1362,22 +1376,24 @@
       <x:c r="E9" t="str">
         <x:v>1. ログインする
 2. 学年1を選ぶ
-3. パート33-2を選んで開始する
-4. 表示順6の問題まで進める（途中で間違えてもOK）
-5. 表示順6の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート19-1を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F9" t="str">
-        <x:v>問題文: Do you go after school?
-期待解答: Where do you go after school?
-画像: 画像なしで問題なし
-指示文: 例にならい、Whereを使った 疑問文を考えましょう。</x:v>
+        <x:v>このパート全体（1-19-1 / 全8問）を最後まで通して確認する。
+最初の問題文: We have lunch at school.
+最初の期待解答: We don't have lunch at school.
+画像: 画像なしのパート
+指示文: 肯定文を否定文に言いかえましょう。</x:v>
       </x:c>
       <x:c r="G9" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H9" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I9" t="str"/>
       <x:c r="J9" t="str"/>
@@ -1385,13 +1401,13 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="str">
-        <x:v>RQ-009</x:v>
+        <x:v>RP-009</x:v>
       </x:c>
       <x:c r="B10" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C10" t="str">
-        <x:v>学年1 / パート36-1 / 1-36-1-5</x:v>
+        <x:v>学年1 / パート23-2 / 1-23-2</x:v>
       </x:c>
       <x:c r="D10" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -1399,22 +1415,24 @@
       <x:c r="E10" t="str">
         <x:v>1. ログインする
 2. 学年1を選ぶ
-3. パート36-1を選んで開始する
-4. 表示順5の問題まで進める（途中で間違えてもOK）
-5. 表示順5の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート23-2を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F10" t="str">
-        <x:v>問題文: What's the plural of child?
-期待解答: It's children.
-画像: 画像なしで問題なし
-指示文: 例にならい、複数形(plural)を答えましょう。</x:v>
+        <x:v>このパート全体（1-23-2 / 全8問）を最後まで通して確認する。
+最初の問題文: Are we in the large park?
+最初の期待解答: Yes, we are. We are in the large park.
+画像: 8問で画像あり
+指示文: イラストの指示に従い、 Yes, またはNo,で質問に答えましょう。</x:v>
       </x:c>
       <x:c r="G10" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H10" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I10" t="str"/>
       <x:c r="J10" t="str"/>
@@ -1422,13 +1440,13 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="str">
-        <x:v>RQ-010</x:v>
+        <x:v>RP-010</x:v>
       </x:c>
       <x:c r="B11" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C11" t="str">
-        <x:v>学年1 / パート36-1 / 1-36-1-6</x:v>
+        <x:v>学年1 / パート30-2 / 1-30-2</x:v>
       </x:c>
       <x:c r="D11" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -1436,22 +1454,24 @@
       <x:c r="E11" t="str">
         <x:v>1. ログインする
 2. 学年1を選ぶ
-3. パート36-1を選んで開始する
-4. 表示順6の問題まで進める（途中で間違えてもOK）
-5. 表示順6の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート30-2を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F11" t="str">
-        <x:v>問題文: What's the plural of family?
-期待解答: It's families.
-画像: 画像なしで問題なし
-指示文: 例にならい、複数形(plural)を答えましょう。</x:v>
+        <x:v>このパート全体（1-30-2 / 全8問）を最後まで通して確認する。
+最初の問題文: What's your favorite drink?
+最初の期待解答: My favorite drink is orange juice.
+画像: 8問で画像あり
+指示文: 例にならい、 イラストを見て問題に答えましょう。</x:v>
       </x:c>
       <x:c r="G11" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H11" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I11" t="str"/>
       <x:c r="J11" t="str"/>
@@ -1459,13 +1479,13 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="str">
-        <x:v>RQ-011</x:v>
+        <x:v>RP-011</x:v>
       </x:c>
       <x:c r="B12" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C12" t="str">
-        <x:v>学年1 / パート36-2 / 1-36-2-5</x:v>
+        <x:v>学年1 / パート37-1 / 1-37-1</x:v>
       </x:c>
       <x:c r="D12" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -1473,22 +1493,24 @@
       <x:c r="E12" t="str">
         <x:v>1. ログインする
 2. 学年1を選ぶ
-3. パート36-2を選んで開始する
-4. 表示順5の問題まで進める（途中で間違えてもOK）
-5. 表示順5の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート37-1を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F12" t="str">
-        <x:v>問題文: What's the plural of fox?
-期待解答: It's foxes.
-画像: 画像なしで問題なし
-指示文: 例にならい、複数形(plural)を答えましょう。</x:v>
+        <x:v>このパート全体（1-37-1 / 全8問）を最後まで通して確認する。
+最初の問題文: Do you write emails?
+最初の期待解答: How many emails do you write?
+画像: 8問で画像あり
+指示文: 例にならい、How many + 名詞を使って、 「どのくらいの～を～しますか？」 とたずねましょう。</x:v>
       </x:c>
       <x:c r="G12" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H12" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I12" t="str"/>
       <x:c r="J12" t="str"/>
@@ -1496,13 +1518,13 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
-        <x:v>RQ-012</x:v>
+        <x:v>RP-012</x:v>
       </x:c>
       <x:c r="B13" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C13" t="str">
-        <x:v>学年1 / パート37-3 / 1-37-3-4</x:v>
+        <x:v>学年1 / パート37-2 / 1-37-2</x:v>
       </x:c>
       <x:c r="D13" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -1510,22 +1532,24 @@
       <x:c r="E13" t="str">
         <x:v>1. ログインする
 2. 学年1を選ぶ
-3. パート37-3を選んで開始する
-4. 表示順4の問題まで進める（途中で間違えてもOK）
-5. 表示順4の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート37-2を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F13" t="str">
-        <x:v>問題文: Is she old?
-期待解答: How old is she?
-画像: /questions/1_37_3_04.png
-指示文: How old を使って、　 人の年齢（ものの古さ）をたずねましょう。</x:v>
+        <x:v>このパート全体（1-37-2 / 全8問）を最後まで通して確認する。
+最初の問題文: Is this a pen?
+最初の期待解答: How long is this pen?
+画像: 8問で画像あり
+指示文: 例にならい、How long を使って、ものや時間の長さをたずねましょう。</x:v>
       </x:c>
       <x:c r="G13" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H13" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I13" t="str"/>
       <x:c r="J13" t="str"/>
@@ -1533,13 +1557,13 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
-        <x:v>RQ-013</x:v>
+        <x:v>RP-013</x:v>
       </x:c>
       <x:c r="B14" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C14" t="str">
-        <x:v>学年1 / パート44-2 / 1-44-2-6</x:v>
+        <x:v>学年1 / パート46-2 / 1-46-2</x:v>
       </x:c>
       <x:c r="D14" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -1547,22 +1571,24 @@
       <x:c r="E14" t="str">
         <x:v>1. ログインする
 2. 学年1を選ぶ
-3. パート44-2を選んで開始する
-4. 表示順6の問題まで進める（途中で間違えてもOK）
-5. 表示順6の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート46-2を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F14" t="str">
-        <x:v>問題文: Who is turning off the light?
-期待解答: I'm turning off the light.
-画像: 画像なしで問題なし
-指示文: 例にならい、だれが～しているのですか？ の問いに私がしています。と答えましょう。</x:v>
+        <x:v>このパート全体（1-46-2 / 全8問）を最後まで通して確認する。
+最初の問題文: She writes a letter.
+最初の期待解答: She wrote a letter last week.
+画像: 8問で画像あり
+指示文: 例にならい、 文を過去形に言いかえましょう。</x:v>
       </x:c>
       <x:c r="G14" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H14" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I14" t="str"/>
       <x:c r="J14" t="str"/>
@@ -1570,13 +1596,13 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
-        <x:v>RQ-014</x:v>
+        <x:v>RP-014</x:v>
       </x:c>
       <x:c r="B15" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C15" t="str">
-        <x:v>学年1 / パート46-2 / 1-46-2-4</x:v>
+        <x:v>学年1 / パート49-1 / 1-49-1</x:v>
       </x:c>
       <x:c r="D15" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -1584,22 +1610,24 @@
       <x:c r="E15" t="str">
         <x:v>1. ログインする
 2. 学年1を選ぶ
-3. パート46-2を選んで開始する
-4. 表示順4の問題まで進める（途中で間違えてもOK）
-5. 表示順4の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート49-1を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F15" t="str">
-        <x:v>問題文: She comes home late.
-期待解答: She came home late last night.
-画像: /questions/1_46_2_04.png
-指示文: 例にならい、 文を過去形に言いかえましょう。</x:v>
+        <x:v>このパート全体（1-49-1 / 全8問）を最後まで通して確認する。
+最初の問題文: I watched something yesterday evening.
+最初の期待解答: What did you watch yesterday evening?
+画像: 画像なしのパート
+指示文: 例にならい、 「What」を使って、「何を～したのですか？」とたずねましょう。</x:v>
       </x:c>
       <x:c r="G15" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H15" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I15" t="str"/>
       <x:c r="J15" t="str"/>
@@ -1607,13 +1635,13 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
-        <x:v>RQ-015</x:v>
+        <x:v>RP-015</x:v>
       </x:c>
       <x:c r="B16" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C16" t="str">
-        <x:v>学年1 / パート50-1 / 1-50-1-2</x:v>
+        <x:v>学年1 / パート50-1 / 1-50-1</x:v>
       </x:c>
       <x:c r="D16" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -1622,21 +1650,23 @@
         <x:v>1. ログインする
 2. 学年1を選ぶ
 3. パート50-1を選んで開始する
-4. 表示順2の問題まで進める（途中で間違えてもOK）
-5. 表示順2の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F16" t="str">
-        <x:v>問題文: You are tired.
-期待解答: You were tired last night.
-画像: /questions/1_50_1_02.png
+        <x:v>このパート全体（1-50-1 / 全8問）を最後まで通して確認する。
+最初の問題文: I am excited.
+最初の期待解答: I was excited yesterday.
+画像: 8問で画像あり
 指示文: 例にならい、現在形の文を「～でした。」 の過去形で答えましょう。</x:v>
       </x:c>
       <x:c r="G16" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H16" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I16" t="str"/>
       <x:c r="J16" t="str"/>
@@ -1644,13 +1674,13 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
-        <x:v>RQ-016</x:v>
+        <x:v>RP-016</x:v>
       </x:c>
       <x:c r="B17" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C17" t="str">
-        <x:v>学年2 / パート3-1 / 2-3-1-8</x:v>
+        <x:v>学年2 / パート7-1 / 2-7-1</x:v>
       </x:c>
       <x:c r="D17" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -1658,22 +1688,24 @@
       <x:c r="E17" t="str">
         <x:v>1. ログインする
 2. 学年2を選ぶ
-3. パート3-1を選んで開始する
-4. 表示順8の問題まで進める（途中で間違えてもOK）
-5. 表示順8の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート7-1を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F17" t="str">
-        <x:v>問題文: The cat sees a bird in the garden.
-期待解答: The cat saw a bird in the garden at night.
-画像: /questions/2_3_1_08.png
-指示文: 例にならい、 現在形の文章を過去形に直しましょう。</x:v>
+        <x:v>このパート全体（2-7-1 / 全8問）を最後まで通して確認する。
+最初の問題文: She was worrying about the test.
+最初の期待解答: She wasn't worrying about the test.
+画像: 画像なしのパート
+指示文: 例にならい、過去進行形の肯定文を、 過去進行形の否定文に直しましょう。</x:v>
       </x:c>
       <x:c r="G17" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H17" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I17" t="str"/>
       <x:c r="J17" t="str"/>
@@ -1681,13 +1713,13 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="str">
-        <x:v>RQ-017</x:v>
+        <x:v>RP-017</x:v>
       </x:c>
       <x:c r="B18" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C18" t="str">
-        <x:v>学年2 / パート6-1 / 2-6-1-2</x:v>
+        <x:v>学年2 / パート14-2 / 2-14-2</x:v>
       </x:c>
       <x:c r="D18" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -1695,22 +1727,24 @@
       <x:c r="E18" t="str">
         <x:v>1. ログインする
 2. 学年2を選ぶ
-3. パート6-1を選んで開始する
-4. 表示順2の問題まで進める（途中で間違えてもOK）
-5. 表示順2の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート14-2を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F18" t="str">
-        <x:v>問題文: I study English.
-期待解答: I'm studying English.
-画像: 画像なしで問題なし
-指示文: 例にならい、現在形の文を 現在進行形に直しましょう。</x:v>
+        <x:v>このパート全体（2-14-2 / 全8問）を最後まで通して確認する。
+最初の問題文: They bake bread every morning.
+最初の期待解答: Will they bake bread every morning?
+画像: 画像なしのパート
+指示文: 現在形の文章を～するでしょうか？と尋ねる 未来を表す疑問文にしましょう。</x:v>
       </x:c>
       <x:c r="G18" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H18" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I18" t="str"/>
       <x:c r="J18" t="str"/>
@@ -1718,13 +1752,13 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="str">
-        <x:v>RQ-018</x:v>
+        <x:v>RP-018</x:v>
       </x:c>
       <x:c r="B19" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C19" t="str">
-        <x:v>学年2 / パート6-1 / 2-6-1-6</x:v>
+        <x:v>学年2 / パート16-2 / 2-16-2</x:v>
       </x:c>
       <x:c r="D19" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -1732,22 +1766,24 @@
       <x:c r="E19" t="str">
         <x:v>1. ログインする
 2. 学年2を選ぶ
-3. パート6-1を選んで開始する
-4. 表示順6の問題まで進める（途中で間違えてもOK）
-5. 表示順6の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート16-2を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F19" t="str">
-        <x:v>問題文: I write a letter.
-期待解答: I'm writing a letter.
-画像: 画像なしで問題なし
-指示文: 例にならい、現在形の文を 現在進行形に直しましょう。</x:v>
+        <x:v>このパート全体（2-16-2 / 全8問）を最後まで通して確認する。
+最初の問題文: How did the story make you feel?
+最初の期待解答: It made me sad.
+画像: 8問で画像あり
+指示文: 【ＡをＢにする】 　make を使った 　質問文に答えましょう。</x:v>
       </x:c>
       <x:c r="G19" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H19" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I19" t="str"/>
       <x:c r="J19" t="str"/>
@@ -1755,13 +1791,13 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="str">
-        <x:v>RQ-019</x:v>
+        <x:v>RP-019</x:v>
       </x:c>
       <x:c r="B20" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C20" t="str">
-        <x:v>学年2 / パート7-1 / 2-7-1-8</x:v>
+        <x:v>学年2 / パート17-2 / 2-17-2</x:v>
       </x:c>
       <x:c r="D20" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -1769,22 +1805,24 @@
       <x:c r="E20" t="str">
         <x:v>1. ログインする
 2. 学年2を選ぶ
-3. パート7-1を選んで開始する
-4. 表示順8の問題まで進める（途中で間違えてもOK）
-5. 表示順8の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート17-2を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F20" t="str">
-        <x:v>問題文: I was checking my homework.
-期待解答: I wasn't checking my homework.
-画像: 画像なしで問題なし
-指示文: 例にならい、過去進行形の肯定文を、 過去進行形の否定文に直しましょう。</x:v>
+        <x:v>このパート全体（2-17-2 / 全8問）を最後まで通して確認する。
+最初の問題文: What did he do when he finished dinner?
+最初の期待解答: He watched TV when he finished dinner.
+画像: 8問で画像あり
+指示文: 「接続詞 "When ～のとき」を使い、ヒントを見て、 そのとき、何をしていたのか説明しましょう。</x:v>
       </x:c>
       <x:c r="G20" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H20" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I20" t="str"/>
       <x:c r="J20" t="str"/>
@@ -1792,13 +1830,13 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="str">
-        <x:v>RQ-020</x:v>
+        <x:v>RP-020</x:v>
       </x:c>
       <x:c r="B21" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C21" t="str">
-        <x:v>学年2 / パート9-2 / 2-9-2-4</x:v>
+        <x:v>学年2 / パート27-2 / 2-27-2</x:v>
       </x:c>
       <x:c r="D21" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -1806,22 +1844,24 @@
       <x:c r="E21" t="str">
         <x:v>1. ログインする
 2. 学年2を選ぶ
-3. パート9-2を選んで開始する
-4. 表示順4の問題まで進める（途中で間違えてもOK）
-5. 表示順4の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート27-2を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F21" t="str">
-        <x:v>問題文: There were some toys on the shelf.
-期待解答: Were there any toys on the shelf?
-画像: 画像なしで問題なし
-指示文: There was There were 「あった、いた」の文を、 疑問文に直しましょう。</x:v>
+        <x:v>このパート全体（2-27-2 / 全8問）を最後まで通して確認する。
+最初の問題文: Why do we practice English?
+最初の期待解答: To speak well.
+画像: 8問で画像あり
+指示文: 【不定詞】例にならい、 質問に「To ＋動詞の原形」で答えよう。</x:v>
       </x:c>
       <x:c r="G21" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H21" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I21" t="str"/>
       <x:c r="J21" t="str"/>
@@ -1829,13 +1869,13 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="str">
-        <x:v>RQ-021</x:v>
+        <x:v>RP-021</x:v>
       </x:c>
       <x:c r="B22" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C22" t="str">
-        <x:v>学年2 / パート11-1 / 2-11-1-2</x:v>
+        <x:v>学年2 / パート33-2 / 2-33-2</x:v>
       </x:c>
       <x:c r="D22" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -1843,22 +1883,24 @@
       <x:c r="E22" t="str">
         <x:v>1. ログインする
 2. 学年2を選ぶ
-3. パート11-1を選んで開始する
-4. 表示順2の問題まで進める（途中で間違えてもOK）
-5. 表示順2の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート33-2を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F22" t="str">
-        <x:v>問題文: You're going to know the answer.
-期待解答: You're not going to know the answer.
-画像: 画像なしで問題なし
-指示文: 未来形の肯定文を not を使い 未来形の否定文にしましょう。</x:v>
+        <x:v>このパート全体（2-33-2 / 全8問）を最後まで通して確認する。
+最初の問題文: Talking about your country.
+最初の期待解答: Which city is the biggest in your country?
+画像: 8問で画像あり
+指示文: イラストを見て、【Which】を使い、 「どちらの～が一番～ですか？」 という疑問文を考えましょう。</x:v>
       </x:c>
       <x:c r="G22" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H22" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I22" t="str"/>
       <x:c r="J22" t="str"/>
@@ -1866,13 +1908,13 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="str">
-        <x:v>RQ-022</x:v>
+        <x:v>RP-022</x:v>
       </x:c>
       <x:c r="B23" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C23" t="str">
-        <x:v>学年2 / パート13-1 / 2-13-1-3</x:v>
+        <x:v>学年2 / パート35-1 / 2-35-1</x:v>
       </x:c>
       <x:c r="D23" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -1880,22 +1922,24 @@
       <x:c r="E23" t="str">
         <x:v>1. ログインする
 2. 学年2を選ぶ
-3. パート13-1を選んで開始する
-4. 表示順3の問題まで進める（途中で間違えてもOK）
-5. 表示順3の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート35-1を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F23" t="str">
-        <x:v>問題文: We borrow books from the library.
-期待解答: We will borrow books from the library.
-画像: 画像なしで問題なし
-指示文: 現在形の文をwillを使って～します。 ～でしょう。などの未来を表す文にしましょう。</x:v>
+        <x:v>このパート全体（2-35-1 / 全8問）を最後まで通して確認する。
+最初の問題文: Which book is more interesting, Jack's book or Emma's book?
+最初の期待解答: Jack's book is more interesting than Emma's book.
+画像: 8問で画像あり
+指示文: 【more】 を使って疑問文に答えましょう。</x:v>
       </x:c>
       <x:c r="G23" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H23" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I23" t="str"/>
       <x:c r="J23" t="str"/>
@@ -1903,13 +1947,13 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="str">
-        <x:v>RQ-023</x:v>
+        <x:v>RP-023</x:v>
       </x:c>
       <x:c r="B24" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C24" t="str">
-        <x:v>学年2 / パート14-1 / 2-14-1-8</x:v>
+        <x:v>学年2 / パート35-2 / 2-35-2</x:v>
       </x:c>
       <x:c r="D24" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -1917,22 +1961,24 @@
       <x:c r="E24" t="str">
         <x:v>1. ログインする
 2. 学年2を選ぶ
-3. パート14-1を選んで開始する
-4. 表示順8の問題まで進める（途中で間違えてもOK）
-5. 表示順8の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート35-2を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F24" t="str">
-        <x:v>問題文: I'm nervous before the test.
-期待解答: I won't be nervous before the test.
-画像: 画像なしで問題なし
-指示文: 現在形の文章を「won't（will not)」を使い ～しないでしょうと言う未来否定文にしましょう。</x:v>
+        <x:v>このパート全体（2-35-2 / 全8問）を最後まで通して確認する。
+最初の問題文: Which is the most beautiful city in Japan?
+最初の期待解答: Kyoto is the most beautiful city in Japan.
+画像: 8問で画像あり
+指示文: 【most】 を使って疑問文に答えましょう。</x:v>
       </x:c>
       <x:c r="G24" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H24" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I24" t="str"/>
       <x:c r="J24" t="str"/>
@@ -1940,13 +1986,13 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="str">
-        <x:v>RQ-024</x:v>
+        <x:v>RP-024</x:v>
       </x:c>
       <x:c r="B25" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C25" t="str">
-        <x:v>学年2 / パート16-2 / 2-16-2-5</x:v>
+        <x:v>学年2 / パート38-2 / 2-38-2</x:v>
       </x:c>
       <x:c r="D25" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -1954,22 +2000,24 @@
       <x:c r="E25" t="str">
         <x:v>1. ログインする
 2. 学年2を選ぶ
-3. パート16-2を選んで開始する
-4. 表示順5の問題まで進める（途中で間違えてもOK）
-5. 表示順5の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート38-2を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F25" t="str">
-        <x:v>問題文: What made the children tired?
-期待解答: The long walk made them tired.
-画像: /questions/2_16_2_05.png
-指示文: 【ＡをＢにする】 　make を使った 　質問文に答えましょう。</x:v>
+        <x:v>このパート全体（2-38-2 / 全8問）を最後まで通して確認する。
+最初の問題文: The police caught the thief.
+最初の期待解答: The thief was caught by the police.
+画像: 画像なしのパート
+指示文: 【受け身】 「例にならって文を受け身にしましょう」</x:v>
       </x:c>
       <x:c r="G25" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H25" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I25" t="str"/>
       <x:c r="J25" t="str"/>
@@ -1977,13 +2025,13 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="str">
-        <x:v>RQ-025</x:v>
+        <x:v>RP-025</x:v>
       </x:c>
       <x:c r="B26" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C26" t="str">
-        <x:v>学年2 / パート30-3 / 2-30-3-3</x:v>
+        <x:v>学年2 / パート39-2 / 2-39-2</x:v>
       </x:c>
       <x:c r="D26" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -1991,22 +2039,24 @@
       <x:c r="E26" t="str">
         <x:v>1. ログインする
 2. 学年2を選ぶ
-3. パート30-3を選んで開始する
-4. 表示順3の問題まで進める（途中で間違えてもOK）
-5. 表示順3の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート39-2を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F26" t="str">
-        <x:v>問題文: What is important for you?
-期待解答: Studying English is important.
-画像: /questions/2_30_3_03.png
-指示文: 例にならい、動名詞を文の主語にして 質問に答えましょう。</x:v>
+        <x:v>このパート全体（2-39-2 / 全8問）を最後まで通して確認する。
+最初の問題文: Someone broke the window.
+最初の期待解答: The window was broken by someone.
+画像: 画像なしのパート
+指示文: 【受け身】② 「例にならって文を受け身にしましょう」</x:v>
       </x:c>
       <x:c r="G26" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H26" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I26" t="str"/>
       <x:c r="J26" t="str"/>
@@ -2014,13 +2064,13 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="str">
-        <x:v>RQ-026</x:v>
+        <x:v>RP-026</x:v>
       </x:c>
       <x:c r="B27" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C27" t="str">
-        <x:v>学年2 / パート31-1 / 2-31-1-6</x:v>
+        <x:v>学年2 / パート43-1 / 2-43-1</x:v>
       </x:c>
       <x:c r="D27" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -2028,22 +2078,24 @@
       <x:c r="E27" t="str">
         <x:v>1. ログインする
 2. 学年2を選ぶ
-3. パート31-1を選んで開始する
-4. 表示順6の問題まで進める（途中で間違えてもOK）
-5. 表示順6の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート43-1を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F27" t="str">
-        <x:v>問題文: I don't make robots.
-期待解答: Do you know how to make a robot?
-画像: 画像なしで問題なし
-指示文: 【不定詞名詞的用法】 Do you know how to make~を使い、 どのようにしたらよいか尋ねる文を考えましょう。</x:v>
+        <x:v>このパート全体（2-43-1 / 全8問）を最後まで通して確認する。
+最初の問題文: How long have you studied English?
+最初の期待解答: I have studied English for three years.
+画像: 8問で画像あり
+指示文: 「How long have you~?どのくらいの期間 あなたは～しているの？」の問いに対して、 「I have ＋過去分詞」を使用し どのくらいの期間～しているのか答えましょう。</x:v>
       </x:c>
       <x:c r="G27" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H27" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I27" t="str"/>
       <x:c r="J27" t="str"/>
@@ -2051,13 +2103,13 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="str">
-        <x:v>RQ-027</x:v>
+        <x:v>RP-027</x:v>
       </x:c>
       <x:c r="B28" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C28" t="str">
-        <x:v>学年2 / パート38-2 / 2-38-2-8</x:v>
+        <x:v>学年2 / パート44-1 / 2-44-1</x:v>
       </x:c>
       <x:c r="D28" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -2065,22 +2117,24 @@
       <x:c r="E28" t="str">
         <x:v>1. ログインする
 2. 学年2を選ぶ
-3. パート38-2を選んで開始する
-4. 表示順8の問題まで進める（途中で間違えてもOK）
-5. 表示順8の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート44-1を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F28" t="str">
-        <x:v>問題文: The boy painted the door.
-期待解答: The door was painted by the boy.
-画像: 画像なしで問題なし
-指示文: 【受け身】 「例にならって文を受け身にしましょう」</x:v>
+        <x:v>このパート全体（2-44-1 / 全8問）を最後まで通して確認する。
+最初の問題文: They have been married since 2020.
+最初の期待解答: They haven't been married since 2020.
+画像: 画像なしのパート
+指示文: 「現在完了形」の文を否定文に直しましょう。</x:v>
       </x:c>
       <x:c r="G28" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H28" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I28" t="str"/>
       <x:c r="J28" t="str"/>
@@ -2088,13 +2142,13 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="str">
-        <x:v>RQ-028</x:v>
+        <x:v>RP-028</x:v>
       </x:c>
       <x:c r="B29" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C29" t="str">
-        <x:v>学年2 / パート42-2 / 2-42-2-3</x:v>
+        <x:v>学年2 / パート44-3 / 2-44-3</x:v>
       </x:c>
       <x:c r="D29" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -2102,22 +2156,24 @@
       <x:c r="E29" t="str">
         <x:v>1. ログインする
 2. 学年2を選ぶ
-3. パート42-2を選んで開始する
-4. 表示順3の問題まで進める（途中で間違えてもOK）
-5. 表示順3の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート44-3を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F29" t="str">
-        <x:v>問題文: Have you ever traveled abroad?
-期待解答: No, I haven't.
-画像: /questions/2_42_2_03.png
-指示文: 「現在完了形」 現在形と現在完了形の疑問文に Noで答えましょう。</x:v>
+        <x:v>このパート全体（2-44-3 / 全8問）を最後まで通して確認する。
+最初の問題文: You live in Tokyo.
+最初の期待解答: How long have you lived in Tokyo?
+画像: 画像なしのパート
+指示文: 例にならい、現在形の文を 「How long have / has ～？」 を使った現在完了形の疑問文に書きかえましょう。</x:v>
       </x:c>
       <x:c r="G29" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H29" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I29" t="str"/>
       <x:c r="J29" t="str"/>
@@ -2125,13 +2181,13 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="str">
-        <x:v>RQ-029</x:v>
+        <x:v>RP-029</x:v>
       </x:c>
       <x:c r="B30" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C30" t="str">
-        <x:v>学年2 / パート45-1 / 2-45-1-2</x:v>
+        <x:v>学年2 / パート45-1 / 2-45-1</x:v>
       </x:c>
       <x:c r="D30" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -2140,21 +2196,23 @@
         <x:v>1. ログインする
 2. 学年2を選ぶ
 3. パート45-1を選んで開始する
-4. 表示順2の問題まで進める（途中で間違えてもOK）
-5. 表示順2の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F30" t="str">
-        <x:v>問題文: They visited Osaka last month.
-期待解答: They have visited Osaka twice.
-画像: /questions/2_45_1_02.png
+        <x:v>このパート全体（2-45-1 / 全8問）を最後まで通して確認する。
+最初の問題文: I met him yesterday.
+最初の期待解答: I have met him three times.
+画像: 8問で画像あり
 指示文: 「現在完了形」②　have + 過去分詞 　 例にならい、過去形の文章を 「～をしたことがある」という経験を 伝える文に直しましょう。</x:v>
       </x:c>
       <x:c r="G30" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H30" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I30" t="str"/>
       <x:c r="J30" t="str"/>
@@ -2162,13 +2220,13 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="str">
-        <x:v>RQ-030</x:v>
+        <x:v>RP-030</x:v>
       </x:c>
       <x:c r="B31" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C31" t="str">
-        <x:v>学年2 / パート47-2 / 2-47-2-5</x:v>
+        <x:v>学年2 / パート45-2 / 2-45-2</x:v>
       </x:c>
       <x:c r="D31" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -2176,22 +2234,24 @@
       <x:c r="E31" t="str">
         <x:v>1. ログインする
 2. 学年2を選ぶ
-3. パート47-2を選んで開始する
-4. 表示順5の問題まで進める（途中で間違えてもOK）
-5. 表示順5の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート45-2を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F31" t="str">
-        <x:v>問題文: Have you washed the dishes yet? I haven't washed the dishes yet.
-期待解答: I haven't broken a cup yet.
-画像: 画像なしで問題なし
-指示文: Have you ～yet?もう～しましたか？ の問いに対して、yet を使い「まだしてないよ」 という文を考えましょう。</x:v>
+        <x:v>このパート全体（2-45-2 / 全8問）を最後まで通して確認する。
+最初の問題文: I went to America five years ago.
+最初の期待解答: I have been to America once.
+画像: 8問で画像あり
+指示文: 「現在完了形」②　  例にならい、 過去形の文章を「～行ったことがある」という 行った経験を伝える文章に直しましょう。</x:v>
       </x:c>
       <x:c r="G31" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H31" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I31" t="str"/>
       <x:c r="J31" t="str"/>
@@ -2199,13 +2259,13 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="str">
-        <x:v>RQ-031</x:v>
+        <x:v>RP-031</x:v>
       </x:c>
       <x:c r="B32" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C32" t="str">
-        <x:v>学年3 / パート6-2 / 3-6-2-6</x:v>
+        <x:v>学年3 / パート2-2 / 3-2-2</x:v>
       </x:c>
       <x:c r="D32" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -2213,22 +2273,24 @@
       <x:c r="E32" t="str">
         <x:v>1. ログインする
 2. 学年3を選ぶ
-3. パート6-2を選んで開始する
-4. 表示順6の問題まで進める（途中で間違えてもOK）
-5. 表示順6の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート2-2を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F32" t="str">
-        <x:v>問題文: The windows were broken by the boys. Were the windows broken by the boys?
-期待解答: Was Apple founded by Steve Jobs?
-画像: 画像なしで問題なし
-指示文: 【受け身】例にならい、 　受け身の文を疑問文に直しましょう。</x:v>
+        <x:v>このパート全体（3-2-2 / 全8問）を最後まで通して確認する。
+最初の問題文: Yumi likes orange juice.
+最初の期待解答: Does she like orange juice?
+画像: 画像なしのパート
+指示文: 例にならって、文を疑問文にかえましょう。　　　　そのとき、主語は代名詞にしましょう。</x:v>
       </x:c>
       <x:c r="G32" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H32" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I32" t="str"/>
       <x:c r="J32" t="str"/>
@@ -2236,13 +2298,13 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33" t="str">
-        <x:v>RQ-032</x:v>
+        <x:v>RP-032</x:v>
       </x:c>
       <x:c r="B33" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C33" t="str">
-        <x:v>学年3 / パート13-1 / 3-13-1-3</x:v>
+        <x:v>学年3 / パート8-2 / 3-8-2</x:v>
       </x:c>
       <x:c r="D33" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -2250,22 +2312,24 @@
       <x:c r="E33" t="str">
         <x:v>1. ログインする
 2. 学年3を選ぶ
-3. パート13-1を選んで開始する
-4. 表示順3の問題まで進める（途中で間違えてもOK）
-5. 表示順3の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート8-2を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F33" t="str">
-        <x:v>問題文: He plays soccer.
-期待解答: He has played soccer since he was five.
-画像: /questions/3_13_1_03.png
-指示文: 現在完了を使って、「（今まで）ずっとしている」　 　の文章に言いかえましょう。</x:v>
+        <x:v>このパート全体（3-8-2 / 全8問）を最後まで通して確認する。
+最初の問題文: I worked here.
+最初の期待解答: I have worked here for two years.
+画像: 8問で画像あり
+指示文: 過去形を現在完了（継続用法）  「～の間ずっと…している」 という文に直しましょう。</x:v>
       </x:c>
       <x:c r="G33" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H33" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I33" t="str"/>
       <x:c r="J33" t="str"/>
@@ -2273,13 +2337,13 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" t="str">
-        <x:v>RQ-033</x:v>
+        <x:v>RP-033</x:v>
       </x:c>
       <x:c r="B34" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C34" t="str">
-        <x:v>学年3 / パート15-1 / 3-15-1-3</x:v>
+        <x:v>学年3 / パート9-2 / 3-9-2</x:v>
       </x:c>
       <x:c r="D34" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -2287,22 +2351,24 @@
       <x:c r="E34" t="str">
         <x:v>1. ログインする
 2. 学年3を選ぶ
-3. パート15-1を選んで開始する
-4. 表示順3の問題まで進める（途中で間違えてもOK）
-5. 表示順3の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート9-2を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F34" t="str">
-        <x:v>問題文: What is exciting to do?
-期待解答: It's exciting to visit a new country.
-画像: /questions/3_15_1_03.png
-指示文: 質問に対して「It is ~  to …」の形で答えましょう。</x:v>
+        <x:v>このパート全体（3-9-2 / 全8問）を最後まで通して確認する。
+最初の問題文: I have finished my homework.
+最初の期待解答: Have you finished your homework?
+画像: 画像なしのパート
+指示文: 「現在完了形」の文を「Have you 」を使い 現在完了の疑問文に直しましょう。</x:v>
       </x:c>
       <x:c r="G34" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H34" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I34" t="str"/>
       <x:c r="J34" t="str"/>
@@ -2310,13 +2376,13 @@
     </x:row>
     <x:row r="35">
       <x:c r="A35" t="str">
-        <x:v>RQ-034</x:v>
+        <x:v>RP-034</x:v>
       </x:c>
       <x:c r="B35" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C35" t="str">
-        <x:v>学年3 / パート15-2 / 3-15-2-6</x:v>
+        <x:v>学年3 / パート13-3 / 3-13-3</x:v>
       </x:c>
       <x:c r="D35" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -2324,22 +2390,24 @@
       <x:c r="E35" t="str">
         <x:v>1. ログインする
 2. 学年3を選ぶ
-3. パート15-2を選んで開始する
-4. 表示順6の問題まで進める（途中で間違えてもOK）
-5. 表示順6の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート13-3を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F35" t="str">
-        <x:v>問題文: What is fun for your sister to do?
-期待解答: It's fun for my sister to play the piano.
-画像: /questions/3_15_2_06.png
-指示文: 質問に対して「It is ~ for 人 to …」 (…することは~にとって~です)の形で答えましょう。</x:v>
+        <x:v>このパート全体（3-13-3 / 全8問）を最後まで通して確認する。
+最初の問題文: I finished my homework.
+最初の期待解答: I have already finished my homework.
+画像: 8問で画像あり
+指示文: 過去形の文を　現在完了「もう～してしまった」 「ちょうど～したところだ」　 という文に直しましょう。</x:v>
       </x:c>
       <x:c r="G35" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H35" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I35" t="str"/>
       <x:c r="J35" t="str"/>
@@ -2347,13 +2415,13 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="str">
-        <x:v>RQ-035</x:v>
+        <x:v>RP-035</x:v>
       </x:c>
       <x:c r="B36" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C36" t="str">
-        <x:v>学年3 / パート16-2 / 3-16-2-8</x:v>
+        <x:v>学年3 / パート14-2 / 3-14-2</x:v>
       </x:c>
       <x:c r="D36" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -2361,22 +2429,24 @@
       <x:c r="E36" t="str">
         <x:v>1. ログインする
 2. 学年3を選ぶ
-3. パート16-2を選んで開始する
-4. 表示順8の問題まで進める（途中で間違えてもOK）
-5. 表示順8の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート14-2を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F36" t="str">
-        <x:v>問題文: I want to win the game.
-期待解答: I'd like to win the game.
-画像: 画像なしで問題なし
-指示文: 例にならい「I'd like "to" ~]を使い 　よりていねいな表現に言いかえましょう。"</x:v>
+        <x:v>このパート全体（3-14-2 / 全8問）を最後まで通して確認する。
+最初の問題文: She draws pictures.
+最初の期待解答: How long has she been drawing pictures?
+画像: 画像なしのパート
+指示文: How long を使って『どのくらい〜し続けていますか?』と たずねる文を作りましょう。主語は代名詞に変えましょう。</x:v>
       </x:c>
       <x:c r="G36" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H36" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I36" t="str"/>
       <x:c r="J36" t="str"/>
@@ -2384,13 +2454,13 @@
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="str">
-        <x:v>RQ-036</x:v>
+        <x:v>RP-036</x:v>
       </x:c>
       <x:c r="B37" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C37" t="str">
-        <x:v>学年3 / パート20-1 / 3-20-1-5</x:v>
+        <x:v>学年3 / パート16-2 / 3-16-2</x:v>
       </x:c>
       <x:c r="D37" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -2398,22 +2468,24 @@
       <x:c r="E37" t="str">
         <x:v>1. ログインする
 2. 学年3を選ぶ
-3. パート20-1を選んで開始する
-4. 表示順5の問題まで進める（途中で間違えてもOK）
-5. 表示順5の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート16-2を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F37" t="str">
-        <x:v>問題文: I'll answer the question.
-期待解答: Let me answer the question.
-画像: 画像なしで問題なし
-指示文: 「I'll ~」の文を「Let me ~」(私に~させて)の形に言いかえましょう。</x:v>
+        <x:v>このパート全体（3-16-2 / 全8問）を最後まで通して確認する。
+最初の問題文: I want to meet you.
+最初の期待解答: I'd like to meet you.
+画像: 画像なしのパート
+指示文: 例にならい「I'd like "to" ~]を使い 　よりていねいな表現に言いかえましょう。"</x:v>
       </x:c>
       <x:c r="G37" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H37" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I37" t="str"/>
       <x:c r="J37" t="str"/>
@@ -2421,13 +2493,13 @@
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="str">
-        <x:v>RQ-037</x:v>
+        <x:v>RP-037</x:v>
       </x:c>
       <x:c r="B38" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C38" t="str">
-        <x:v>学年3 / パート21-2 / 3-21-2-6</x:v>
+        <x:v>学年3 / パート17-1 / 3-17-1</x:v>
       </x:c>
       <x:c r="D38" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -2435,22 +2507,24 @@
       <x:c r="E38" t="str">
         <x:v>1. ログインする
 2. 学年3を選ぶ
-3. パート21-2を選んで開始する
-4. 表示順6の問題まで進める（途中で間違えてもOK）
-5. 表示順6の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート17-1を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F38" t="str">
-        <x:v>問題文: How does a horror story make you feel?
-期待解答: It makes me afraid.
-画像: /questions/3_21_2_06.png
-指示文: 例にならい、make + 人 + 形容詞 「(人)を〜な気持ちにさせる」の形を使って、 気持ちを表す文を考えましょう。</x:v>
+        <x:v>このパート全体（3-17-1 / 全8問）を最後まで通して確認する。
+最初の問題文: Do you want some help?
+最初の期待解答: Would you like some help?
+画像: 画像なしのパート
+指示文: 例にならい「Would you like ~」を使い 　よりていねいな表現に言いかえましょう。</x:v>
       </x:c>
       <x:c r="G38" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H38" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I38" t="str"/>
       <x:c r="J38" t="str"/>
@@ -2458,13 +2532,13 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" t="str">
-        <x:v>RQ-038</x:v>
+        <x:v>RP-038</x:v>
       </x:c>
       <x:c r="B39" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C39" t="str">
-        <x:v>学年3 / パート25-1 / 3-25-1-6</x:v>
+        <x:v>学年3 / パート18-2 / 3-18-2</x:v>
       </x:c>
       <x:c r="D39" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -2472,22 +2546,24 @@
       <x:c r="E39" t="str">
         <x:v>1. ログインする
 2. 学年3を選ぶ
-3. パート25-1を選んで開始する
-4. 表示順6の問題まで進める（途中で間違えてもOK）
-5. 表示順6の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート18-2を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F39" t="str">
-        <x:v>問題文: Who is the boy playing soccer?
-期待解答: The boy playing soccer is Bob.
-画像: /questions/3_25_1_06.png
-指示文: 例にならい、質問に対して「The ~」　から始まる文で答えましょう。</x:v>
+        <x:v>このパート全体（3-18-2 / 全8問）を最後まで通して確認する。
+最初の問題文: I want you to help me.
+最初の期待解答: Do you want me to help you?
+画像: 画像なしのパート
+指示文: 「I want you to ~」の文を「Do you want me to ~?」 (私が~しましょうか?) の形に変えて答えましょう。 代名詞は適切に変えましょう。</x:v>
       </x:c>
       <x:c r="G39" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H39" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I39" t="str"/>
       <x:c r="J39" t="str"/>
@@ -2495,13 +2571,13 @@
     </x:row>
     <x:row r="40">
       <x:c r="A40" t="str">
-        <x:v>RQ-039</x:v>
+        <x:v>RP-039</x:v>
       </x:c>
       <x:c r="B40" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C40" t="str">
-        <x:v>学年3 / パート25-2 / 3-25-2-8</x:v>
+        <x:v>学年3 / パート21-1 / 3-21-1</x:v>
       </x:c>
       <x:c r="D40" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -2509,22 +2585,24 @@
       <x:c r="E40" t="str">
         <x:v>1. ログインする
 2. 学年3を選ぶ
-3. パート25-2を選んで開始する
-4. 表示順8の問題まで進める（途中で間違えてもOK）
-5. 表示順8の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート21-1を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F40" t="str">
-        <x:v>問題文: Which girl are you pointing at?
-期待解答: I'm pointing at the girl talking on the phone.
-画像: /questions/3_25_2_08.png
-指示文: 例にならい、質問に答えましょう。</x:v>
+        <x:v>このパート全体（3-21-1 / 全8問）を最後まで通して確認する。
+最初の問題文: What did she name her baby?
+最初の期待解答: She named her Rin.
+画像: 8問で画像あり
+指示文: 「name(~と名づける)」「call(~と呼ぶ)」を使って答えましょう。 主語が固有名詞や「her baby」などの場合は代名詞に変えましょう。</x:v>
       </x:c>
       <x:c r="G40" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H40" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I40" t="str"/>
       <x:c r="J40" t="str"/>
@@ -2532,13 +2610,13 @@
     </x:row>
     <x:row r="41">
       <x:c r="A41" t="str">
-        <x:v>RQ-040</x:v>
+        <x:v>RP-040</x:v>
       </x:c>
       <x:c r="B41" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C41" t="str">
-        <x:v>学年3 / パート27-1 / 3-27-1-2</x:v>
+        <x:v>学年3 / パート25-2 / 3-25-2</x:v>
       </x:c>
       <x:c r="D41" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -2546,22 +2624,24 @@
       <x:c r="E41" t="str">
         <x:v>1. ログインする
 2. 学年3を選ぶ
-3. パート27-1を選んで開始する
-4. 表示順2の問題まで進める（途中で間違えてもOK）
-5. 表示順2の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート25-2を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F41" t="str">
-        <x:v>問題文: the temple
-期待解答: the temple we visited in Kyoto
-画像: /questions/3_27_1_02.png
-指示文: 例にならい、名詞を「主語＋動詞〜」で後ろから説明する形にしましょう。 動詞は過去形にしましょう。</x:v>
+        <x:v>このパート全体（3-25-2 / 全8問）を最後まで通して確認する。
+最初の問題文: Which boy are you looking for?
+最初の期待解答: I'm looking for the boy running in the park.
+画像: 8問で画像あり
+指示文: 例にならい、質問に答えましょう。</x:v>
       </x:c>
       <x:c r="G41" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H41" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I41" t="str"/>
       <x:c r="J41" t="str"/>
@@ -2569,13 +2649,13 @@
     </x:row>
     <x:row r="42">
       <x:c r="A42" t="str">
-        <x:v>RQ-041</x:v>
+        <x:v>RP-041</x:v>
       </x:c>
       <x:c r="B42" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C42" t="str">
-        <x:v>学年3 / パート27-1 / 3-27-1-3</x:v>
+        <x:v>学年3 / パート27-2 / 3-27-2</x:v>
       </x:c>
       <x:c r="D42" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -2583,22 +2663,24 @@
       <x:c r="E42" t="str">
         <x:v>1. ログインする
 2. 学年3を選ぶ
-3. パート27-1を選んで開始する
-4. 表示順3の問題まで進める（途中で間違えてもOK）
-5. 表示順3の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート27-2を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F42" t="str">
-        <x:v>問題文: the woman
-期待解答: the woman he met at the station
-画像: /questions/3_27_1_03.png
-指示文: 例にならい、名詞を「主語＋動詞〜」で後ろから説明する形にしましょう。 動詞は過去形にしましょう。</x:v>
+        <x:v>このパート全体（3-27-2 / 全8問）を最後まで通して確認する。
+最初の問題文: I read a book. The book was interesting.
+最初の期待解答: The book I read was interesting.
+画像: 画像なしのパート
+指示文: 前文の名詞を、後文の内容を使って 「名詞＋主語＋動詞」の形で1文にしましょう。 ※ 関係代名詞は使いません。</x:v>
       </x:c>
       <x:c r="G42" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H42" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I42" t="str"/>
       <x:c r="J42" t="str"/>
@@ -2606,13 +2688,13 @@
     </x:row>
     <x:row r="43">
       <x:c r="A43" t="str">
-        <x:v>RQ-042</x:v>
+        <x:v>RP-042</x:v>
       </x:c>
       <x:c r="B43" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C43" t="str">
-        <x:v>学年3 / パート27-2 / 3-27-2-2</x:v>
+        <x:v>学年3 / パート28-2 / 3-28-2</x:v>
       </x:c>
       <x:c r="D43" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -2620,22 +2702,24 @@
       <x:c r="E43" t="str">
         <x:v>1. ログインする
 2. 学年3を選ぶ
-3. パート27-2を選んで開始する
-4. 表示順2の問題まで進める（途中で間違えてもOK）
-5. 表示順2の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート28-2を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F43" t="str">
-        <x:v>問題文: She met a man. The man was kind.
-期待解答: The man she met was kind.
-画像: 画像なしで問題なし
-指示文: 前文の名詞を、後文の内容を使って 「名詞＋主語＋動詞」の形で1文にしましょう。 ※ 関係代名詞は使いません。</x:v>
+        <x:v>このパート全体（3-28-2 / 全8問）を最後まで通して確認する。
+最初の問題文: She is a girl. She plays the piano.
+最初の期待解答: She is a girl who plays the piano.
+画像: 画像なしのパート
+指示文: 【確認問題】例にならい、2つの文を関係代名詞 「who」 を使って、1つの文に直しましょう。</x:v>
       </x:c>
       <x:c r="G43" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H43" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I43" t="str"/>
       <x:c r="J43" t="str"/>
@@ -2643,13 +2727,13 @@
     </x:row>
     <x:row r="44">
       <x:c r="A44" t="str">
-        <x:v>RQ-043</x:v>
+        <x:v>RP-043</x:v>
       </x:c>
       <x:c r="B44" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C44" t="str">
-        <x:v>学年3 / パート33-2 / 3-33-2-7</x:v>
+        <x:v>学年3 / パート30-2 / 3-30-2</x:v>
       </x:c>
       <x:c r="D44" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -2657,22 +2741,24 @@
       <x:c r="E44" t="str">
         <x:v>1. ログインする
 2. 学年3を選ぶ
-3. パート33-2を選んで開始する
-4. 表示順7の問題まで進める（途中で間違えてもOK）
-5. 表示順7の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート30-2を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F44" t="str">
-        <x:v>問題文: This room is big.
-期待解答: I wish this room were big.
-画像: 画像なしで問題なし
-指示文: 例にならい、文を「I wish ～」実際の事実とは違う 「〜だったらいいのに」 という気持ちを表す文に書きかえましょう。</x:v>
+        <x:v>このパート全体（3-30-2 / 全8問）を最後まで通して確認する。
+最初の問題文: He painted a picture. The picture is very famous.
+最初の期待解答: The picture that he painted is very famous.
+画像: 画像なしのパート
+指示文: 次の2つの文を、関係代名詞【that】を使って1つの文にしましょう。 答えは「The 〜」から始めましょう。</x:v>
       </x:c>
       <x:c r="G44" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H44" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I44" t="str"/>
       <x:c r="J44" t="str"/>
@@ -2680,13 +2766,13 @@
     </x:row>
     <x:row r="45">
       <x:c r="A45" t="str">
-        <x:v>RQ-044</x:v>
+        <x:v>RP-044</x:v>
       </x:c>
       <x:c r="B45" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C45" t="str">
-        <x:v>学年3 / パート34-2 / 3-34-2-5</x:v>
+        <x:v>学年3 / パート31-3 / 3-31-3</x:v>
       </x:c>
       <x:c r="D45" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -2694,22 +2780,24 @@
       <x:c r="E45" t="str">
         <x:v>1. ログインする
 2. 学年3を選ぶ
-3. パート34-2を選んで開始する
-4. 表示順5の問題まで進める（途中で間違えてもOK）
-5. 表示順5の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート31-3を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F45" t="str">
-        <x:v>問題文: You are a robot.
-期待解答: If you were a robot, you would never get tired.
-画像: /questions/3_34_2_05.png
-指示文: 「If 主語 were ～, 主語 would ～.」の形に 言いかえましょう。</x:v>
+        <x:v>このパート全体（3-31-3 / 全8問）を最後まで通して確認する。
+最初の問題文: He painted a picture. The picture is very famous.
+最初の期待解答: The picture that he painted is very famous.
+画像: 画像なしのパート
+指示文: 例にならい、 2つの文を、関係代名詞 that を使って1つの文にしましょう。 答えは「The 〜」から始めましょう。</x:v>
       </x:c>
       <x:c r="G45" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H45" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I45" t="str"/>
       <x:c r="J45" t="str"/>
@@ -2717,13 +2805,13 @@
     </x:row>
     <x:row r="46">
       <x:c r="A46" t="str">
-        <x:v>RQ-045</x:v>
+        <x:v>RP-045</x:v>
       </x:c>
       <x:c r="B46" t="str">
         <x:v>ランダム問題</x:v>
       </x:c>
       <x:c r="C46" t="str">
-        <x:v>学年3 / パート35-1 / 3-35-1-2</x:v>
+        <x:v>学年3 / パート32-2 / 3-32-2</x:v>
       </x:c>
       <x:c r="D46" t="str">
         <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
@@ -2731,22 +2819,24 @@
       <x:c r="E46" t="str">
         <x:v>1. ログインする
 2. 学年3を選ぶ
-3. パート35-1を選んで開始する
-4. 表示順2の問題まで進める（途中で間違えてもOK）
-5. 表示順2の画面で、問題文・画像・音声・解答後の動きを確認する
-6. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
+3. パート32-2を選んで開始する
+4. このパートを最初から最後までプレイする（全8問）
+5. 途中で間違えてもOK。最後の結果画面まで進めるか確認する
+6. プレイ中に問題文・画像・音声・解答後の動き・次問遷移をざっと確認する
+7. 確認が終わったら判定列にOK/NG/保留を記入する</x:v>
       </x:c>
       <x:c r="F46" t="str">
-        <x:v>問題文: I should study abroad.
-期待解答: If I were you, I would study abroad.
-画像: 画像なしで問題なし
-指示文: 「If I were you～, I would ～.」の形に 言いかえましょう。</x:v>
+        <x:v>このパート全体（3-32-2 / 全8問）を最後まで通して確認する。
+最初の問題文: If I get money, I'll buy it.
+最初の期待解答: If I got money, I would buy it.
+画像: 画像なしのパート
+指示文: 例にならい、「現実の話（will）」を 　「空想の話（would）」に言いかえてみましょう。</x:v>
       </x:c>
       <x:c r="G46" t="str">
-        <x:v>対象の問題まで進める。No Dataや白画面にならない。問題文・指示文・画像が上記内容と大きくズレない。音声再生後、解答して次へ進める。</x:v>
+        <x:v>パートを開始でき、全問プレイして結果画面まで進める。No Dataや白画面にならない。問題文・指示文・画像・音声に明らかな欠落がなく、解答後に次の問題へ進める。</x:v>
       </x:c>
       <x:c r="H46" t="str">
-        <x:v>対象の問題まで進めない / No Dataが出る / 画面が固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に進まない。</x:v>
+        <x:v>パートを開始できない / 途中でNo Dataが出る / 途中で固まる / 画像が壊れる / 問題文が空 / 音声が鳴らない / 解答後に次へ進まない / 結果画面まで行けない。</x:v>
       </x:c>
       <x:c r="I46" t="str"/>
       <x:c r="J46" t="str"/>

--- a/outputs/Mukaさん_外注テストケース_2026-06-12.xlsx
+++ b/outputs/Mukaさん_外注テストケース_2026-06-12.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_概要" sheetId="1" r:id="R87c1dfe53ab640fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_事前説明" sheetId="2" r:id="R48cc71de191d49bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_基本操作" sheetId="3" r:id="R2c10618b3c67438d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_ランダム問題" sheetId="4" r:id="Rb77c857a74d042a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_要望回帰" sheetId="5" r:id="R2d0e4715de934e09"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_バグ報告" sheetId="6" r:id="R266dd85221164df9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_概要" sheetId="1" r:id="Rc232b9268dce4a15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_事前説明" sheetId="2" r:id="R86d1661d6e7c4167"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_基本操作" sheetId="3" r:id="R2c3c424d9f1d445b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_ランダム問題" sheetId="4" r:id="Re6f110ed84fe40dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_要望回帰" sheetId="5" r:id="Re1f8f42e8f2b4684"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_バグ報告" sheetId="6" r:id="Rf16c5d3ac2354ec1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2853,15 +2853,18 @@
   <x:cols>
     <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="26" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="58" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="58" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="48" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="44" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="32" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="26" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="34" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="58" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="58" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="48" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="44" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="32" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -2872,30 +2875,39 @@
         <x:v>テスト種別</x:v>
       </x:c>
       <x:c r="C1" s="8" t="str">
+        <x:v>要望区分</x:v>
+      </x:c>
+      <x:c r="D1" s="8" t="str">
+        <x:v>要望No</x:v>
+      </x:c>
+      <x:c r="E1" s="8" t="str">
+        <x:v>要望日</x:v>
+      </x:c>
+      <x:c r="F1" s="8" t="str">
         <x:v>対象画面・パート</x:v>
       </x:c>
-      <x:c r="D1" s="8" t="str">
+      <x:c r="G1" s="8" t="str">
         <x:v>事前準備</x:v>
       </x:c>
-      <x:c r="E1" s="8" t="str">
+      <x:c r="H1" s="8" t="str">
         <x:v>操作手順</x:v>
       </x:c>
-      <x:c r="F1" s="8" t="str">
+      <x:c r="I1" s="8" t="str">
         <x:v>確認すること</x:v>
       </x:c>
-      <x:c r="G1" s="8" t="str">
+      <x:c r="J1" s="8" t="str">
         <x:v>OK条件</x:v>
       </x:c>
-      <x:c r="H1" s="8" t="str">
+      <x:c r="K1" s="8" t="str">
         <x:v>NG例</x:v>
       </x:c>
-      <x:c r="I1" s="8" t="str">
+      <x:c r="L1" s="8" t="str">
         <x:v>判定（テスター記入）</x:v>
       </x:c>
-      <x:c r="J1" s="8" t="str">
+      <x:c r="M1" s="8" t="str">
         <x:v>メモ（テスター記入）</x:v>
       </x:c>
-      <x:c r="K1" s="8" t="str">
+      <x:c r="N1" s="8" t="str">
         <x:v>バグ報告No（テスター記入）</x:v>
       </x:c>
     </x:row>
@@ -2907,31 +2919,40 @@
         <x:v>要望回帰</x:v>
       </x:c>
       <x:c r="C2" t="str">
+        <x:v>機能・仕様要望</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E2" t="str">
+        <x:v>2026-06-03</x:v>
+      </x:c>
+      <x:c r="F2" t="str">
         <x:v>1-1-1</x:v>
       </x:c>
-      <x:c r="D2" t="str">
-        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
-      </x:c>
-      <x:c r="E2" t="str">
+      <x:c r="G2" t="str">
+        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
+      </x:c>
+      <x:c r="H2" t="str">
         <x:v>1. ログインする
 2. 対象パート/問題を開く
 3. 元要望欄に書かれている動きを試す
 4. うまく認識されるか、認識されにくいかをメモに書く
 5. 進行不能や明らかなエラーがある場合だけ保留にしてスクショ/録画を添付する</x:v>
       </x:c>
-      <x:c r="F2" t="str">
+      <x:c r="I2" t="str">
         <x:v>元要望: １－１－1-全体的に（特に8番）答えを認識してもらえない
 対応内容: こちらの対応記録が確認できていないため、状況を再調査のうえ改めてご連絡します。※解答の判定は完全一致ではなく類似度62%以上で正解としていますが、1-1-1は1単語(Iなど)のみの解答のため音声認識が誤認識しやすい箇所です</x:v>
       </x:c>
-      <x:c r="G2" t="str">
+      <x:c r="J2" t="str">
         <x:v>この行は要確認のためOK/NGを無理に判断しない。実際の挙動をメモに書く。</x:v>
       </x:c>
-      <x:c r="H2" t="str">
+      <x:c r="K2" t="str">
         <x:v>進行不能・明らかなエラー・判断不能の場合は保留にしてスクショ/録画を添付。</x:v>
       </x:c>
-      <x:c r="I2" t="str"/>
-      <x:c r="J2" t="str"/>
-      <x:c r="K2" t="str"/>
+      <x:c r="L2" t="str"/>
+      <x:c r="M2" t="str"/>
+      <x:c r="N2" t="str"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
@@ -2941,30 +2962,39 @@
         <x:v>要望回帰</x:v>
       </x:c>
       <x:c r="C3" t="str">
+        <x:v>機能・仕様要望</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="E3" t="str">
+        <x:v>2026-03-15</x:v>
+      </x:c>
+      <x:c r="F3" t="str">
         <x:v>機能・仕様要望 No.135</x:v>
       </x:c>
-      <x:c r="D3" t="str">
-        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
-      </x:c>
-      <x:c r="E3" t="str">
+      <x:c r="G3" t="str">
+        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
+      </x:c>
+      <x:c r="H3" t="str">
         <x:v>1. ログイン画面を開く
 2. 元要望に書かれている状況を再現する
 3. 対応内容欄のとおり、表示や動きが改善されているか確認する
 4. 迷う表示・遅すぎる表示・進めない状態があればNGにする</x:v>
       </x:c>
-      <x:c r="F3" t="str">
+      <x:c r="I3" t="str">
         <x:v>元要望: ログイン画面でログインボタンを押すと、ボタンの色が変わる、または音が出る使用に出来ますか？反応がまだ遅く、反応しているの分からず何度もボタンを押してしまう。
 対応内容: LOGINボタンを押すと「Logging in...」表示に切り替わり、処理中は再度押せないようにしました。5秒以上かかる場合は「サーバー起動中です」の案内も表示されます</x:v>
       </x:c>
-      <x:c r="G3" t="str">
+      <x:c r="J3" t="str">
         <x:v>対応内容どおりに動作し、元要望と同じ不具合が再発しない。</x:v>
       </x:c>
-      <x:c r="H3" t="str">
+      <x:c r="K3" t="str">
         <x:v>元要望と同じ不具合が起きる / 対応内容と違う / 操作できない / 画面が崩れる。</x:v>
       </x:c>
-      <x:c r="I3" t="str"/>
-      <x:c r="J3" t="str"/>
-      <x:c r="K3" t="str"/>
+      <x:c r="L3" t="str"/>
+      <x:c r="M3" t="str"/>
+      <x:c r="N3" t="str"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
@@ -2974,30 +3004,39 @@
         <x:v>要望回帰</x:v>
       </x:c>
       <x:c r="C4" t="str">
+        <x:v>機能・仕様要望</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="E4" t="str">
+        <x:v>2026-04-21</x:v>
+      </x:c>
+      <x:c r="F4" t="str">
         <x:v>機能・仕様要望 No.139</x:v>
       </x:c>
-      <x:c r="D4" t="str">
-        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
-      </x:c>
-      <x:c r="E4" t="str">
+      <x:c r="G4" t="str">
+        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
+      </x:c>
+      <x:c r="H4" t="str">
         <x:v>1. ログイン画面を開く
 2. 元要望に書かれている状況を再現する
 3. 対応内容欄のとおり、表示や動きが改善されているか確認する
 4. 迷う表示・遅すぎる表示・進めない状態があればNGにする</x:v>
       </x:c>
-      <x:c r="F4" t="str">
+      <x:c r="I4" t="str">
         <x:v>元要望: 長い間ログインしていないと、認証が必要です。と画面に出ますが、再度リンクを探してログインし直すしか方法はないのでしょうか？ログインしなおしてください。など実際にしなければならないことを、書いてあったら分かりやすいかなと思います。
 対応内容: 認証切れの際のメッセージを「ログインの有効期限が切れています。再度ログインしてください」のように、実際に行うことが分かる文言に統一しました</x:v>
       </x:c>
-      <x:c r="G4" t="str">
+      <x:c r="J4" t="str">
         <x:v>対応内容どおりに動作し、元要望と同じ不具合が再発しない。</x:v>
       </x:c>
-      <x:c r="H4" t="str">
+      <x:c r="K4" t="str">
         <x:v>元要望と同じ不具合が起きる / 対応内容と違う / 操作できない / 画面が崩れる。</x:v>
       </x:c>
-      <x:c r="I4" t="str"/>
-      <x:c r="J4" t="str"/>
-      <x:c r="K4" t="str"/>
+      <x:c r="L4" t="str"/>
+      <x:c r="M4" t="str"/>
+      <x:c r="N4" t="str"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="str">
@@ -3007,30 +3046,39 @@
         <x:v>要望回帰</x:v>
       </x:c>
       <x:c r="C5" t="str">
+        <x:v>機能・仕様要望</x:v>
+      </x:c>
+      <x:c r="D5" t="str">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="E5" t="str">
+        <x:v>2026-04-23</x:v>
+      </x:c>
+      <x:c r="F5" t="str">
         <x:v>機能・仕様要望 No.140</x:v>
       </x:c>
-      <x:c r="D5" t="str">
-        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
-      </x:c>
-      <x:c r="E5" t="str">
+      <x:c r="G5" t="str">
+        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
+      </x:c>
+      <x:c r="H5" t="str">
         <x:v>1. ログインする
 2. 元要望欄に書かれている画面または操作を探す
 3. 対応内容欄のとおり改善されているか確認する
 4. 判断に迷う場合は保留にして、スクショを添付する</x:v>
       </x:c>
-      <x:c r="F5" t="str">
+      <x:c r="I5" t="str">
         <x:v>元要望: 一日画面を開いたまま、次の日続きをしようとすると、ステージ画面のスタートを押してもゲームの続きができず、承認が必要です。と言われます。そこから承認画面にいくことが出来るようにすることは出来ますか？
 対応内容: 原因はiPadのSafariが一定期間で認証情報(Cookie)を破棄する仕様でした。通信方式を変更してこの問題自体を解消しています。認証切れになった場合も「再度ログインしてください」と案内が表示されます</x:v>
       </x:c>
-      <x:c r="G5" t="str">
+      <x:c r="J5" t="str">
         <x:v>対応内容どおりに動作し、元要望と同じ不具合が再発しない。</x:v>
       </x:c>
-      <x:c r="H5" t="str">
+      <x:c r="K5" t="str">
         <x:v>元要望と同じ不具合が起きる / 対応内容と違う / 操作できない / 画面が崩れる。</x:v>
       </x:c>
-      <x:c r="I5" t="str"/>
-      <x:c r="J5" t="str"/>
-      <x:c r="K5" t="str"/>
+      <x:c r="L5" t="str"/>
+      <x:c r="M5" t="str"/>
+      <x:c r="N5" t="str"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="str">
@@ -3040,31 +3088,40 @@
         <x:v>要望回帰</x:v>
       </x:c>
       <x:c r="C6" t="str">
+        <x:v>機能・仕様要望</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>2026-05-08</x:v>
+      </x:c>
+      <x:c r="F6" t="str">
         <x:v>3-8-1 / 3-8-2 / 1-24-1 / 1-25-1</x:v>
       </x:c>
-      <x:c r="D6" t="str">
-        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
-      </x:c>
-      <x:c r="E6" t="str">
+      <x:c r="G6" t="str">
+        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
+      </x:c>
+      <x:c r="H6" t="str">
         <x:v>1. ログインする
 2. 対象パート/問題（3-8-1 / 3-8-2 / 1-24-1 / 1-25-1）を開く
 3. 元要望欄に書かれている不具合や要望内容を確認する
 4. 対応内容欄のとおり改善されているか確認する
 5. 同じ不具合が再発したらNGにする</x:v>
       </x:c>
-      <x:c r="F6" t="str">
+      <x:c r="I6" t="str">
         <x:v>元要望: 3-8-1 の問題に3-8-２を付け足すことは可能でしょうか？また、今はイラストがない状態なのですが、今からイラストを足すことはできますか？
 対応内容: 3-8-2を新設し、問題8問・解答・イラスト8枚を追加しました。イラストは1-24-1/1-25-1にも追加済みです。※現在はローカル環境での反映のため、ご確認後に本番へ反映します</x:v>
       </x:c>
-      <x:c r="G6" t="str">
+      <x:c r="J6" t="str">
         <x:v>対応内容どおりに動作し、元要望と同じ不具合が再発しない。</x:v>
       </x:c>
-      <x:c r="H6" t="str">
+      <x:c r="K6" t="str">
         <x:v>元要望と同じ不具合が起きる / 対応内容と違う / 操作できない / 画面が崩れる。</x:v>
       </x:c>
-      <x:c r="I6" t="str"/>
-      <x:c r="J6" t="str"/>
-      <x:c r="K6" t="str"/>
+      <x:c r="L6" t="str"/>
+      <x:c r="M6" t="str"/>
+      <x:c r="N6" t="str"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
@@ -3074,31 +3131,40 @@
         <x:v>要望回帰</x:v>
       </x:c>
       <x:c r="C7" t="str">
+        <x:v>機能・仕様要望</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>2026-05-10</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
         <x:v>3-18-1-1 / 3-19-1-1</x:v>
       </x:c>
-      <x:c r="D7" t="str">
-        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
-      </x:c>
-      <x:c r="E7" t="str">
+      <x:c r="G7" t="str">
+        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
+      </x:c>
+      <x:c r="H7" t="str">
         <x:v>1. ログインする
 2. 対象パート/問題（3-18-1-1 / 3-19-1-1）を開く
 3. 元要望欄に書かれている不具合や要望内容を確認する
 4. 対応内容欄のとおり改善されているか確認する
 5. 同じ不具合が再発したらNGにする</x:v>
       </x:c>
-      <x:c r="F7" t="str">
+      <x:c r="I7" t="str">
         <x:v>元要望: 3-18-1-1 、3-19-1-1 … ～～2回読まれるはずの回答条件が、1度しか読まれませんでした。
 対応内容: 音声の取得に失敗した場合に自動で再取得するようにし、2回読み上げが欠けないようにしました(No146と同じ対応)</x:v>
       </x:c>
-      <x:c r="G7" t="str">
+      <x:c r="J7" t="str">
         <x:v>対応内容どおりに動作し、元要望と同じ不具合が再発しない。</x:v>
       </x:c>
-      <x:c r="H7" t="str">
+      <x:c r="K7" t="str">
         <x:v>元要望と同じ不具合が起きる / 対応内容と違う / 操作できない / 画面が崩れる。</x:v>
       </x:c>
-      <x:c r="I7" t="str"/>
-      <x:c r="J7" t="str"/>
-      <x:c r="K7" t="str"/>
+      <x:c r="L7" t="str"/>
+      <x:c r="M7" t="str"/>
+      <x:c r="N7" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="str">
@@ -3108,31 +3174,40 @@
         <x:v>要望回帰</x:v>
       </x:c>
       <x:c r="C8" t="str">
+        <x:v>機能・仕様要望</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="E8" t="str">
+        <x:v>2026-05-11</x:v>
+      </x:c>
+      <x:c r="F8" t="str">
         <x:v>3-23-2-1 / 3-23-2</x:v>
       </x:c>
-      <x:c r="D8" t="str">
-        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
-      </x:c>
-      <x:c r="E8" t="str">
+      <x:c r="G8" t="str">
+        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
+      </x:c>
+      <x:c r="H8" t="str">
         <x:v>1. ログインする
 2. 対象パート/問題（3-23-2-1 / 3-23-2）を開く
 3. 元要望欄に書かれている不具合や要望内容を確認する
 4. 対応内容欄のとおり改善されているか確認する
 5. 同じ不具合が再発したらNGにする</x:v>
       </x:c>
-      <x:c r="F8" t="str">
+      <x:c r="I8" t="str">
         <x:v>元要望: 3-23-2-1~8 問題文が7番までしか読まれませんでした。
 対応内容: 音声取得失敗時の自動再取得(No146と同じ対応)に加え、完成版データで3-23-2の全8問が正しく出題されることを自動チェックで確認しました</x:v>
       </x:c>
-      <x:c r="G8" t="str">
+      <x:c r="J8" t="str">
         <x:v>対応内容どおりに動作し、元要望と同じ不具合が再発しない。</x:v>
       </x:c>
-      <x:c r="H8" t="str">
+      <x:c r="K8" t="str">
         <x:v>元要望と同じ不具合が起きる / 対応内容と違う / 操作できない / 画面が崩れる。</x:v>
       </x:c>
-      <x:c r="I8" t="str"/>
-      <x:c r="J8" t="str"/>
-      <x:c r="K8" t="str"/>
+      <x:c r="L8" t="str"/>
+      <x:c r="M8" t="str"/>
+      <x:c r="N8" t="str"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="str">
@@ -3142,33 +3217,42 @@
         <x:v>要望回帰</x:v>
       </x:c>
       <x:c r="C9" t="str">
+        <x:v>不具合・改善報告</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="E9" t="str">
+        <x:v>2026-03-14</x:v>
+      </x:c>
+      <x:c r="F9" t="str">
         <x:v>1-24-1 / 1-24-2 / 1-25-1</x:v>
       </x:c>
-      <x:c r="D9" t="str">
-        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
-      </x:c>
-      <x:c r="E9" t="str">
+      <x:c r="G9" t="str">
+        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
+      </x:c>
+      <x:c r="H9" t="str">
         <x:v>1. ログインする
 2. 対象パート/問題（1-24-1 / 1-24-2 / 1-25-1）を開く
 3. 元要望欄に書かれている不具合や要望内容を確認する
 4. 対応内容欄のとおり改善されているか確認する
 5. 同じ不具合が再発したらNGにする</x:v>
       </x:c>
-      <x:c r="F9" t="str">
+      <x:c r="I9" t="str">
         <x:v>元要望: 1-24-1- コンピューターからの質問、回答の音声,が出ませんでした。
 1-24-2- こちらも同じく
 1-25-1-こちらもです
 対応内容: 完成版データで1-24-1/1-24-2/1-25-1の問題文・解答を整備し、1-24-1/1-25-1のイラストを追加しました。音声はTTSで合成されます。※1-24-2のイラストは未提供のため画像なしで動作します(提供あり次第追加可能)</x:v>
       </x:c>
-      <x:c r="G9" t="str">
+      <x:c r="J9" t="str">
         <x:v>対応内容どおりに動作し、元要望と同じ不具合が再発しない。</x:v>
       </x:c>
-      <x:c r="H9" t="str">
+      <x:c r="K9" t="str">
         <x:v>元要望と同じ不具合が起きる / 対応内容と違う / 操作できない / 画面が崩れる。</x:v>
       </x:c>
-      <x:c r="I9" t="str"/>
-      <x:c r="J9" t="str"/>
-      <x:c r="K9" t="str"/>
+      <x:c r="L9" t="str"/>
+      <x:c r="M9" t="str"/>
+      <x:c r="N9" t="str"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="str">
@@ -3178,30 +3262,39 @@
         <x:v>要望回帰</x:v>
       </x:c>
       <x:c r="C10" t="str">
+        <x:v>不具合・改善報告</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="E10" t="str">
+        <x:v>2026-03-14</x:v>
+      </x:c>
+      <x:c r="F10" t="str">
         <x:v>不具合・改善報告 No.133</x:v>
       </x:c>
-      <x:c r="D10" t="str">
-        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
-      </x:c>
-      <x:c r="E10" t="str">
+      <x:c r="G10" t="str">
+        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
+      </x:c>
+      <x:c r="H10" t="str">
         <x:v>1. ログインする
 2. 元要望欄に書かれている画面または操作を探す
 3. 対応内容欄のとおり改善されているか確認する
 4. 判断に迷う場合は保留にして、スクショを添付する</x:v>
       </x:c>
-      <x:c r="F10" t="str">
+      <x:c r="I10" t="str">
         <x:v>元要望: ゲーム終了後Score が表示される画面で、あと何問正解でクリア！と書いている個所の、あと何問部分が誤っている。７問中４問正解と出て、あと６問でクリアと出た。
 対応内容: クリアまでの残り問題数の計算を修正しました(あと[5-正解数]問正解でクリア!と表示)。実機で確認済みです</x:v>
       </x:c>
-      <x:c r="G10" t="str">
+      <x:c r="J10" t="str">
         <x:v>対応内容どおりに動作し、元要望と同じ不具合が再発しない。</x:v>
       </x:c>
-      <x:c r="H10" t="str">
+      <x:c r="K10" t="str">
         <x:v>元要望と同じ不具合が起きる / 対応内容と違う / 操作できない / 画面が崩れる。</x:v>
       </x:c>
-      <x:c r="I10" t="str"/>
-      <x:c r="J10" t="str"/>
-      <x:c r="K10" t="str"/>
+      <x:c r="L10" t="str"/>
+      <x:c r="M10" t="str"/>
+      <x:c r="N10" t="str"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="str">
@@ -3211,31 +3304,40 @@
         <x:v>要望回帰</x:v>
       </x:c>
       <x:c r="C11" t="str">
+        <x:v>不具合・改善報告</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>2026-03-14</x:v>
+      </x:c>
+      <x:c r="F11" t="str">
         <x:v>1-25-1-7</x:v>
       </x:c>
-      <x:c r="D11" t="str">
-        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
-      </x:c>
-      <x:c r="E11" t="str">
+      <x:c r="G11" t="str">
+        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
+      </x:c>
+      <x:c r="H11" t="str">
         <x:v>1. ログインする
 2. 対象パート/問題（1-25-1-7）を開く
 3. 元要望欄に書かれている不具合や要望内容を確認する
 4. 対応内容欄のとおり改善されているか確認する
 5. 同じ不具合が再発したらNGにする</x:v>
       </x:c>
-      <x:c r="F11" t="str">
+      <x:c r="I11" t="str">
         <x:v>元要望: 1-25-1-7 制限時間ぎりぎりまで問題を解いていたら、制限時間が切れたあと固まってしまい、次の画面に進めなくなった。No118では画面にボタンを追加と記載されているが見当たらない。
 対応内容: 画面停止時の回復ダイアログを改善しました(リトライ/次の問題へ/やめる の3択)。検知時間も30秒→20秒に短縮し、生徒が考えている時間を停止と誤判定しないようにしました</x:v>
       </x:c>
-      <x:c r="G11" t="str">
+      <x:c r="J11" t="str">
         <x:v>対応内容どおりに動作し、元要望と同じ不具合が再発しない。</x:v>
       </x:c>
-      <x:c r="H11" t="str">
+      <x:c r="K11" t="str">
         <x:v>元要望と同じ不具合が起きる / 対応内容と違う / 操作できない / 画面が崩れる。</x:v>
       </x:c>
-      <x:c r="I11" t="str"/>
-      <x:c r="J11" t="str"/>
-      <x:c r="K11" t="str"/>
+      <x:c r="L11" t="str"/>
+      <x:c r="M11" t="str"/>
+      <x:c r="N11" t="str"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="str">
@@ -3245,30 +3347,39 @@
         <x:v>要望回帰</x:v>
       </x:c>
       <x:c r="C12" t="str">
+        <x:v>不具合・改善報告</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>2026-04-16</x:v>
+      </x:c>
+      <x:c r="F12" t="str">
         <x:v>不具合・改善報告 No.136</x:v>
       </x:c>
-      <x:c r="D12" t="str">
-        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
-      </x:c>
-      <x:c r="E12" t="str">
+      <x:c r="G12" t="str">
+        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
+      </x:c>
+      <x:c r="H12" t="str">
         <x:v>1. ログイン画面を開く
 2. 元要望に書かれている状況を再現する
 3. 対応内容欄のとおり、表示や動きが改善されているか確認する
 4. 迷う表示・遅すぎる表示・進めない状態があればNGにする</x:v>
       </x:c>
-      <x:c r="F12" t="str">
+      <x:c r="I12" t="str">
         <x:v>元要望: ログインにまだ1分ほどかかってしまうのですが、１，２秒でログインすることは難しいでしょうか？
 対応内容: ログイン画面を開いた時点でサーバーを事前起動するようにし、待ち時間を短縮しました。5秒以上かかる場合は「サーバー起動中です」の案内を表示します。※完全な解消にはサーバープランの変更が必要なため、納品時にご相談します</x:v>
       </x:c>
-      <x:c r="G12" t="str">
+      <x:c r="J12" t="str">
         <x:v>対応内容どおりに動作し、元要望と同じ不具合が再発しない。</x:v>
       </x:c>
-      <x:c r="H12" t="str">
+      <x:c r="K12" t="str">
         <x:v>元要望と同じ不具合が起きる / 対応内容と違う / 操作できない / 画面が崩れる。</x:v>
       </x:c>
-      <x:c r="I12" t="str"/>
-      <x:c r="J12" t="str"/>
-      <x:c r="K12" t="str"/>
+      <x:c r="L12" t="str"/>
+      <x:c r="M12" t="str"/>
+      <x:c r="N12" t="str"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
@@ -3278,30 +3389,39 @@
         <x:v>要望回帰</x:v>
       </x:c>
       <x:c r="C13" t="str">
+        <x:v>不具合・改善報告</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>2026-04-19</x:v>
+      </x:c>
+      <x:c r="F13" t="str">
         <x:v>不具合・改善報告 No.137</x:v>
       </x:c>
-      <x:c r="D13" t="str">
-        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
-      </x:c>
-      <x:c r="E13" t="str">
+      <x:c r="G13" t="str">
+        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
+      </x:c>
+      <x:c r="H13" t="str">
         <x:v>1. ログインする
 2. 元要望欄に書かれている画面または操作を探す
 3. 対応内容欄のとおり改善されているか確認する
 4. 判断に迷う場合は保留にして、スクショを添付する</x:v>
       </x:c>
-      <x:c r="F13" t="str">
+      <x:c r="I13" t="str">
         <x:v>元要望: 1－３６－2－3　の問題で固まりました。やはりskip to next questionの表示に時間がかかりました。30～1分くらいかかってしまったので、もう少し早めに出てくれたら安心します。
 対応内容: 画面停止の検知を20秒に短縮し、「次の問題へ」ボタンを含む回復ダイアログがすぐ表示されるようにしました</x:v>
       </x:c>
-      <x:c r="G13" t="str">
+      <x:c r="J13" t="str">
         <x:v>対応内容どおりに動作し、元要望と同じ不具合が再発しない。</x:v>
       </x:c>
-      <x:c r="H13" t="str">
+      <x:c r="K13" t="str">
         <x:v>元要望と同じ不具合が起きる / 対応内容と違う / 操作できない / 画面が崩れる。</x:v>
       </x:c>
-      <x:c r="I13" t="str"/>
-      <x:c r="J13" t="str"/>
-      <x:c r="K13" t="str"/>
+      <x:c r="L13" t="str"/>
+      <x:c r="M13" t="str"/>
+      <x:c r="N13" t="str"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
@@ -3311,32 +3431,41 @@
         <x:v>要望回帰</x:v>
       </x:c>
       <x:c r="C14" t="str">
+        <x:v>不具合・改善報告</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>2026-04-20</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
         <x:v>1-39-2-2</x:v>
       </x:c>
-      <x:c r="D14" t="str">
-        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
-      </x:c>
-      <x:c r="E14" t="str">
+      <x:c r="G14" t="str">
+        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
+      </x:c>
+      <x:c r="H14" t="str">
         <x:v>1. ログインする
 2. 対象パート/問題（1-39-2-2）を開く
 3. 元要望欄に書かれている不具合や要望内容を確認する
 4. 対応内容欄のとおり改善されているか確認する
 5. 同じ不具合が再発したらNGにする</x:v>
       </x:c>
-      <x:c r="F14" t="str">
+      <x:c r="I14" t="str">
         <x:v>元要望: 1-39-2-2 I read this book. readが過去形の発音になっています。
 原形の発音にしていただきたい。
 対応内容: readを現在形(リード)で発音するよう修正しました。修正前に作られた音声キャッシュも無効化したため、確実に新しい発音になります</x:v>
       </x:c>
-      <x:c r="G14" t="str">
+      <x:c r="J14" t="str">
         <x:v>対応内容どおりに動作し、元要望と同じ不具合が再発しない。</x:v>
       </x:c>
-      <x:c r="H14" t="str">
+      <x:c r="K14" t="str">
         <x:v>元要望と同じ不具合が起きる / 対応内容と違う / 操作できない / 画面が崩れる。</x:v>
       </x:c>
-      <x:c r="I14" t="str"/>
-      <x:c r="J14" t="str"/>
-      <x:c r="K14" t="str"/>
+      <x:c r="L14" t="str"/>
+      <x:c r="M14" t="str"/>
+      <x:c r="N14" t="str"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
@@ -3346,30 +3475,39 @@
         <x:v>要望回帰</x:v>
       </x:c>
       <x:c r="C15" t="str">
+        <x:v>不具合・改善報告</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>2026-04-27</x:v>
+      </x:c>
+      <x:c r="F15" t="str">
         <x:v>不具合・改善報告 No.141</x:v>
       </x:c>
-      <x:c r="D15" t="str">
-        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
-      </x:c>
-      <x:c r="E15" t="str">
+      <x:c r="G15" t="str">
+        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
+      </x:c>
+      <x:c r="H15" t="str">
         <x:v>1. ログインする
 2. 元要望欄に書かれている画面または操作を探す
 3. 対応内容欄のとおり改善されているか確認する
 4. 判断に迷う場合は保留にして、スクショを添付する</x:v>
       </x:c>
-      <x:c r="F15" t="str">
+      <x:c r="I15" t="str">
         <x:v>元要望: 2年生の問題になると急に、問題の画面でイラストと問題文が重なることが多々あるのですが、ずらすなどして重ならないようにいただくことは可能でしょうか？
 対応内容: イラストがある問題では、問題文を左側・イラストを右側に分けて表示するレイアウトに変更し、どの画面サイズでも重ならないようにしました</x:v>
       </x:c>
-      <x:c r="G15" t="str">
+      <x:c r="J15" t="str">
         <x:v>対応内容どおりに動作し、元要望と同じ不具合が再発しない。</x:v>
       </x:c>
-      <x:c r="H15" t="str">
+      <x:c r="K15" t="str">
         <x:v>元要望と同じ不具合が起きる / 対応内容と違う / 操作できない / 画面が崩れる。</x:v>
       </x:c>
-      <x:c r="I15" t="str"/>
-      <x:c r="J15" t="str"/>
-      <x:c r="K15" t="str"/>
+      <x:c r="L15" t="str"/>
+      <x:c r="M15" t="str"/>
+      <x:c r="N15" t="str"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
@@ -3379,32 +3517,41 @@
         <x:v>要望回帰</x:v>
       </x:c>
       <x:c r="C16" t="str">
+        <x:v>不具合・改善報告</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>2026-04-30</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
         <x:v>2-22-1-7 / 2-24-1-2</x:v>
       </x:c>
-      <x:c r="D16" t="str">
-        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
-      </x:c>
-      <x:c r="E16" t="str">
+      <x:c r="G16" t="str">
+        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
+      </x:c>
+      <x:c r="H16" t="str">
         <x:v>1. ログインする
 2. 対象パート/問題（2-22-1-7 / 2-24-1-2）を開く
 3. 元要望欄に書かれている不具合や要望内容を確認する
 4. 対応内容欄のとおり改善されているか確認する
 5. 同じ不具合が再発したらNGにする</x:v>
       </x:c>
-      <x:c r="F16" t="str">
+      <x:c r="I16" t="str">
         <x:v>元要望: 2-22-1-7 /2-24-1-2   I read this book.
 They read this book. read の発音が過去形の発音になってます。現在形の発音に変更できますでしょうか？
 対応内容: No138と同じ対応です。readは現在形(リード)で発音されます</x:v>
       </x:c>
-      <x:c r="G16" t="str">
+      <x:c r="J16" t="str">
         <x:v>対応内容どおりに動作し、元要望と同じ不具合が再発しない。</x:v>
       </x:c>
-      <x:c r="H16" t="str">
+      <x:c r="K16" t="str">
         <x:v>元要望と同じ不具合が起きる / 対応内容と違う / 操作できない / 画面が崩れる。</x:v>
       </x:c>
-      <x:c r="I16" t="str"/>
-      <x:c r="J16" t="str"/>
-      <x:c r="K16" t="str"/>
+      <x:c r="L16" t="str"/>
+      <x:c r="M16" t="str"/>
+      <x:c r="N16" t="str"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
@@ -3414,31 +3561,40 @@
         <x:v>要望回帰</x:v>
       </x:c>
       <x:c r="C17" t="str">
+        <x:v>不具合・改善報告</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>2026-05-04</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
         <x:v>2-47-2-1</x:v>
       </x:c>
-      <x:c r="D17" t="str">
-        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
-      </x:c>
-      <x:c r="E17" t="str">
+      <x:c r="G17" t="str">
+        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
+      </x:c>
+      <x:c r="H17" t="str">
         <x:v>1. ログインする
 2. 対象パート/問題（2-47-2-1）を開く
 3. 元要望欄に書かれている不具合や要望内容を確認する
 4. 対応内容欄のとおり改善されているか確認する
 5. 同じ不具合が再発したらNGにする</x:v>
       </x:c>
-      <x:c r="F17" t="str">
+      <x:c r="I17" t="str">
         <x:v>元要望: 2-47-2-1 問題文初めの音が聞こえなかった
 対応内容: 音声の先頭に0.2秒の無音を追加し、再生前に読み込み完了を待つようにしたため、冒頭の音が欠けなくなりました</x:v>
       </x:c>
-      <x:c r="G17" t="str">
+      <x:c r="J17" t="str">
         <x:v>対応内容どおりに動作し、元要望と同じ不具合が再発しない。</x:v>
       </x:c>
-      <x:c r="H17" t="str">
+      <x:c r="K17" t="str">
         <x:v>元要望と同じ不具合が起きる / 対応内容と違う / 操作できない / 画面が崩れる。</x:v>
       </x:c>
-      <x:c r="I17" t="str"/>
-      <x:c r="J17" t="str"/>
-      <x:c r="K17" t="str"/>
+      <x:c r="L17" t="str"/>
+      <x:c r="M17" t="str"/>
+      <x:c r="N17" t="str"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="str">
@@ -3448,31 +3604,40 @@
         <x:v>要望回帰</x:v>
       </x:c>
       <x:c r="C18" t="str">
+        <x:v>不具合・改善報告</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>2026-05-10</x:v>
+      </x:c>
+      <x:c r="F18" t="str">
         <x:v>3-20-1-3</x:v>
       </x:c>
-      <x:c r="D18" t="str">
-        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
-      </x:c>
-      <x:c r="E18" t="str">
+      <x:c r="G18" t="str">
+        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
+      </x:c>
+      <x:c r="H18" t="str">
         <x:v>1. ログインする
 2. 対象パート/問題（3-20-1-3）を開く
 3. 元要望欄に書かれている不具合や要望内容を確認する
 4. 対応内容欄のとおり改善されているか確認する
 5. 同じ不具合が再発したらNGにする</x:v>
       </x:c>
-      <x:c r="F18" t="str">
+      <x:c r="I18" t="str">
         <x:v>元要望: 3-20-1-3  問題文が1回しか読まれませんでした
 対応内容: 音声の取得に失敗した場合に自動で再取得するようにし、2回読み上げが欠けないようにしました</x:v>
       </x:c>
-      <x:c r="G18" t="str">
+      <x:c r="J18" t="str">
         <x:v>対応内容どおりに動作し、元要望と同じ不具合が再発しない。</x:v>
       </x:c>
-      <x:c r="H18" t="str">
+      <x:c r="K18" t="str">
         <x:v>元要望と同じ不具合が起きる / 対応内容と違う / 操作できない / 画面が崩れる。</x:v>
       </x:c>
-      <x:c r="I18" t="str"/>
-      <x:c r="J18" t="str"/>
-      <x:c r="K18" t="str"/>
+      <x:c r="L18" t="str"/>
+      <x:c r="M18" t="str"/>
+      <x:c r="N18" t="str"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="str">
@@ -3482,31 +3647,40 @@
         <x:v>要望回帰</x:v>
       </x:c>
       <x:c r="C19" t="str">
+        <x:v>不具合・改善報告</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
         <x:v>2026-05-12</x:v>
       </x:c>
-      <x:c r="D19" t="str">
-        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
-      </x:c>
-      <x:c r="E19" t="str">
+      <x:c r="F19" t="str">
+        <x:v>2026-05-12</x:v>
+      </x:c>
+      <x:c r="G19" t="str">
+        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
+      </x:c>
+      <x:c r="H19" t="str">
         <x:v>1. ログインする
 2. 対象パート/問題（2026-05-12）を開く
 3. 元要望欄に書かれている不具合や要望内容を確認する
 4. 対応内容欄のとおり改善されているか確認する
 5. 同じ不具合が再発したらNGにする</x:v>
       </x:c>
-      <x:c r="F19" t="str">
+      <x:c r="I19" t="str">
         <x:v>元要望: 3-24からNo Data となっており、問題が出力されません。
 対応内容: 2026-05-12に対応済み・ご確認済みの件です。完成版データでも全パートが正しく出題されることを自動チェックで確認しました</x:v>
       </x:c>
-      <x:c r="G19" t="str">
+      <x:c r="J19" t="str">
         <x:v>対応内容どおりに動作し、元要望と同じ不具合が再発しない。</x:v>
       </x:c>
-      <x:c r="H19" t="str">
+      <x:c r="K19" t="str">
         <x:v>元要望と同じ不具合が起きる / 対応内容と違う / 操作できない / 画面が崩れる。</x:v>
       </x:c>
-      <x:c r="I19" t="str"/>
-      <x:c r="J19" t="str"/>
-      <x:c r="K19" t="str"/>
+      <x:c r="L19" t="str"/>
+      <x:c r="M19" t="str"/>
+      <x:c r="N19" t="str"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="str">
@@ -3516,31 +3690,40 @@
         <x:v>要望回帰</x:v>
       </x:c>
       <x:c r="C20" t="str">
+        <x:v>不具合・改善報告</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>2026-05-16</x:v>
+      </x:c>
+      <x:c r="F20" t="str">
         <x:v>3-34-2 / 2026-05-28</x:v>
       </x:c>
-      <x:c r="D20" t="str">
-        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
-      </x:c>
-      <x:c r="E20" t="str">
+      <x:c r="G20" t="str">
+        <x:v>テスト用URL、ログインID、パスワードを手元に用意。PC Chromeで実施。スマホ指定がある場合のみスマホでも確認。</x:v>
+      </x:c>
+      <x:c r="H20" t="str">
         <x:v>1. ログインする
 2. 対象パート/問題（3-34-2 / 2026-05-28）を開く
 3. 元要望欄に書かれている不具合や要望内容を確認する
 4. 対応内容欄のとおり改善されているか確認する
 5. 同じ不具合が再発したらNGにする</x:v>
       </x:c>
-      <x:c r="F20" t="str">
+      <x:c r="I20" t="str">
         <x:v>元要望: 3-34-2 1~8: 答えが認識されずらい。改善できますでしょうか？
 対応内容: 2026-05-28にMukaさんに再確認いただき問題ないことを確認済みです。今回の修正依頼反映で解答パターンも最新化しています</x:v>
       </x:c>
-      <x:c r="G20" t="str">
+      <x:c r="J20" t="str">
         <x:v>対応内容どおりに動作し、元要望と同じ不具合が再発しない。</x:v>
       </x:c>
-      <x:c r="H20" t="str">
+      <x:c r="K20" t="str">
         <x:v>元要望と同じ不具合が起きる / 対応内容と違う / 操作できない / 画面が崩れる。</x:v>
       </x:c>
-      <x:c r="I20" t="str"/>
-      <x:c r="J20" t="str"/>
-      <x:c r="K20" t="str"/>
+      <x:c r="L20" t="str"/>
+      <x:c r="M20" t="str"/>
+      <x:c r="N20" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
